--- a/04_Figures/F1/c_data/F1.xlsx
+++ b/04_Figures/F1/c_data/F1.xlsx
@@ -656,7 +656,7 @@
     <t>02_HRvLR/01_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>e893235f4b5f4bcc6d90e734d17538c3</t>
+    <t>13a22822b5138c9cba237b44f432c400</t>
   </si>
   <si>
     <t>BiocManager</t>

--- a/04_Figures/F1/c_data/F1.xlsx
+++ b/04_Figures/F1/c_data/F1.xlsx
@@ -11,17 +11,18 @@
     <sheet name="columns" sheetId="2" r:id="rId2"/>
     <sheet name="a_design" sheetId="3" r:id="rId3"/>
     <sheet name="b_pca" sheetId="4" r:id="rId4"/>
-    <sheet name="c_counts" sheetId="5" r:id="rId5"/>
-    <sheet name="d_fry_transfer" sheetId="6" r:id="rId6"/>
-    <sheet name="input_manifest" sheetId="7" r:id="rId7"/>
-    <sheet name="package_versions" sheetId="8" r:id="rId8"/>
+    <sheet name="c_trait_effects" sheetId="5" r:id="rId5"/>
+    <sheet name="d_counts" sheetId="6" r:id="rId6"/>
+    <sheet name="e_fry_transfer" sheetId="7" r:id="rId7"/>
+    <sheet name="input_manifest" sheetId="8" r:id="rId8"/>
+    <sheet name="package_versions" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="361">
   <si>
     <t>sheet</t>
   </si>
@@ -44,19 +45,25 @@
     <t>b_pca</t>
   </si>
   <si>
-    <t>Panel b: PC1 and PC2 per biopsy within each time point, with that time point's PERMANOVA.</t>
-  </si>
-  <si>
-    <t>c_counts</t>
-  </si>
-  <si>
-    <t>Panel c: per contrast and direction, proteins at Π &lt; 0.05, p &lt; 0.05 and FDR &lt; 0.05.</t>
-  </si>
-  <si>
-    <t>d_fry_transfer</t>
-  </si>
-  <si>
-    <t>Panel d: each group's training and acute sets (Π or p &lt; 0.05) tested with fry in the other group's contrast; sets under 5 proteins were not tested.</t>
+    <t>Panel b: PC1 and PC2 per biopsy within each time point, with that time point's PERMANOVA, gap k and forced-split adjusted Rand index.</t>
+  </si>
+  <si>
+    <t>c_trait_effects</t>
+  </si>
+  <si>
+    <t>Panel c: T1 to T2 % change per trait and group with 95% CI (t-test on log ratios), and the HR - LR difference (Welch).</t>
+  </si>
+  <si>
+    <t>d_counts</t>
+  </si>
+  <si>
+    <t>Panel d: per contrast and direction, proteins at Π &lt; 0.05, p &lt; 0.05 and FDR &lt; 0.05.</t>
+  </si>
+  <si>
+    <t>e_fry_transfer</t>
+  </si>
+  <si>
+    <t>Panel e: each group's training and acute sets (Π or p &lt; 0.05) tested with fry in the other group's contrast; sets under 5 proteins were not tested.</t>
   </si>
   <si>
     <t>input_manifest</t>
@@ -77,6 +84,30 @@
     <t>meaning</t>
   </si>
   <si>
+    <t>n_people</t>
+  </si>
+  <si>
+    <t>People analysed.</t>
+  </si>
+  <si>
+    <t>n_hr</t>
+  </si>
+  <si>
+    <t>HR people analysed.</t>
+  </si>
+  <si>
+    <t>n_lr</t>
+  </si>
+  <si>
+    <t>LR people analysed.</t>
+  </si>
+  <si>
+    <t>n_biopsies</t>
+  </si>
+  <si>
+    <t>Biopsies analysed.</t>
+  </si>
+  <si>
     <t>asset</t>
   </si>
   <si>
@@ -95,30 +126,6 @@
     <t>Height of the design image in pixels.</t>
   </si>
   <si>
-    <t>n_people</t>
-  </si>
-  <si>
-    <t>People analysed.</t>
-  </si>
-  <si>
-    <t>n_hr</t>
-  </si>
-  <si>
-    <t>HR people analysed.</t>
-  </si>
-  <si>
-    <t>n_lr</t>
-  </si>
-  <si>
-    <t>LR people analysed.</t>
-  </si>
-  <si>
-    <t>n_biopsies</t>
-  </si>
-  <si>
-    <t>Biopsies analysed.</t>
-  </si>
-  <si>
     <t>timepoint</t>
   </si>
   <si>
@@ -185,15 +192,96 @@
     <t>PERMANOVA p for HR/LR at that time point.</t>
   </si>
   <si>
+    <t>k_gap</t>
+  </si>
+  <si>
+    <t>Clusters the gap statistic picks (one-standard-error rule, k = 1 to 6); 1 means no natural clusters.</t>
+  </si>
+  <si>
+    <t>ari_group</t>
+  </si>
+  <si>
+    <t>Adjusted Rand index between a forced two-cluster PAM split and HR/LR: 1 a perfect match, about 0 chance.</t>
+  </si>
+  <si>
+    <t>trait</t>
+  </si>
+  <si>
+    <t>Phenotype trait: a level (fcsa_mixed, fcsa_type1, fcsa_type2 in um2, mcsa in cm2, leg_press_1rm, leg_ext_1rm in kg), its % change T1 to T2 (pct_ prefix), comp_hypertrophy (composite score) or volume_load_total_kg.</t>
+  </si>
+  <si>
+    <t>used_for_groups</t>
+  </si>
+  <si>
+    <t>Whether the trait enters the composite hypertrophy score that formed the groups (muscle area and mixed fibre area).</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>People with both T1 and T2 values (both groups for HR - LR).</t>
+  </si>
+  <si>
+    <t>pct_change</t>
+  </si>
+  <si>
+    <t>T1 to T2 change as a geometric-mean %; for HR - LR, HR's ratio over LR's, as %.</t>
+  </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>Lower 95% confidence limit of pct_change.</t>
+  </si>
+  <si>
+    <t>upper</t>
+  </si>
+  <si>
+    <t>Upper 95% confidence limit of pct_change.</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>Nominal p-value of the row's test.</t>
+  </si>
+  <si>
+    <t>hr_lr_pct</t>
+  </si>
+  <si>
+    <t>HR's T1 to T2 ratio over LR's, as %.</t>
+  </si>
+  <si>
+    <t>hr_lr_p</t>
+  </si>
+  <si>
+    <t>Welch's t-test of HR against LR on the log ratios; printed beside traits not used to form the groups.</t>
+  </si>
+  <si>
+    <t>block</t>
+  </si>
+  <si>
+    <t>Row block: traits that formed the groups (muscle area, mixed fibre area) or not.</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>Readable feature name: gene symbol, set name or module colour.</t>
+  </si>
+  <si>
+    <t>called</t>
+  </si>
+  <si>
+    <t>Whether the group's change reaches p &lt; 0.05 (filled point).</t>
+  </si>
+  <si>
     <t>family</t>
   </si>
   <si>
     <t>Contrast family the row sits under: Training, Acute, HR - LR or Interaction.</t>
   </si>
   <si>
-    <t>label</t>
-  </si>
-  <si>
     <t>Row label: the group for a within-group window; the time point for HR - LR; the window for an interaction.</t>
   </si>
   <si>
@@ -296,12 +384,6 @@
     <t>Direction fry reports for the set in the other group's contrast.</t>
   </si>
   <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>Nominal p-value of the row's test.</t>
-  </si>
-  <si>
     <t>fdr</t>
   </si>
   <si>
@@ -584,6 +666,52 @@
     <t>S30_T3</t>
   </si>
   <si>
+    <t>fcsa_mixed</t>
+  </si>
+  <si>
+    <t>formed the groups</t>
+  </si>
+  <si>
+    <t>fCSA mixed</t>
+  </si>
+  <si>
+    <t>mcsa</t>
+  </si>
+  <si>
+    <t>mCSA</t>
+  </si>
+  <si>
+    <t>fcsa_type1</t>
+  </si>
+  <si>
+    <t>not used to form them</t>
+  </si>
+  <si>
+    <t>fCSA type1
+HR - LR p 0.0028</t>
+  </si>
+  <si>
+    <t>fcsa_type2</t>
+  </si>
+  <si>
+    <t>fCSA type2
+HR - LR p 0.001</t>
+  </si>
+  <si>
+    <t>leg_press_1rm</t>
+  </si>
+  <si>
+    <t>leg press 1RM
+HR - LR p 0.85</t>
+  </si>
+  <si>
+    <t>leg_ext_1rm</t>
+  </si>
+  <si>
+    <t>leg ext 1RM
+HR - LR p 0.43</t>
+  </si>
+  <si>
     <t>Training</t>
   </si>
   <si>
@@ -656,7 +784,25 @@
     <t>02_HRvLR/01_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>13a22822b5138c9cba237b44f432c400</t>
+    <t>6fd1b8cad619c14e15d908ba9386c1cd</t>
+  </si>
+  <si>
+    <t>variance</t>
+  </si>
+  <si>
+    <t>02_HRvLR/04_Variance/c_data/variance.xlsx</t>
+  </si>
+  <si>
+    <t>8db87e5737d2b9edc64b992b017740a5</t>
+  </si>
+  <si>
+    <t>slopes</t>
+  </si>
+  <si>
+    <t>02_HRvLR/07_Group_Trait_Slopes/c_data/group_trait_slopes.xlsx</t>
+  </si>
+  <si>
+    <t>f24590e2277ed08b7470c1cb8b4f4eee</t>
   </si>
   <si>
     <t>BiocManager</t>
@@ -1305,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -1370,6 +1516,14 @@
       </c>
       <c r="B8" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1379,7 +1533,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -1387,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1398,10 +1552,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1409,10 +1563,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1420,10 +1574,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1431,10 +1585,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1442,10 +1596,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1453,10 +1607,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1464,10 +1618,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1475,10 +1629,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1486,10 +1640,10 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1497,10 +1651,10 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1508,10 +1662,10 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1519,10 +1673,10 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1530,10 +1684,10 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1541,10 +1695,10 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1552,10 +1706,10 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1563,10 +1717,10 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1574,10 +1728,10 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1585,32 +1739,32 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1618,10 +1772,10 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1629,10 +1783,10 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1640,10 +1794,10 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1692,7 +1846,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
         <v>72</v>
@@ -1703,7 +1857,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
         <v>74</v>
@@ -1714,7 +1868,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
         <v>76</v>
@@ -1725,7 +1879,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
         <v>78</v>
@@ -1736,7 +1890,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
         <v>80</v>
@@ -1747,7 +1901,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
         <v>82</v>
@@ -1772,10 +1926,10 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
         <v>86</v>
-      </c>
-      <c r="C36" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1783,10 +1937,10 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s">
         <v>88</v>
-      </c>
-      <c r="C37" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1794,7 +1948,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
         <v>90</v>
@@ -1857,7 +2011,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
         <v>101</v>
@@ -1868,7 +2022,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
         <v>103</v>
@@ -1912,7 +2066,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
         <v>111</v>
@@ -1923,7 +2077,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
         <v>113</v>
@@ -1934,13 +2088,178 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
         <v>115</v>
       </c>
       <c r="C51" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>117</v>
+      </c>
+      <c r="C52" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>89</v>
+      </c>
+      <c r="C53" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" t="s">
+        <v>134</v>
+      </c>
+      <c r="C62" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>16</v>
+      </c>
+      <c r="B64" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>16</v>
+      </c>
+      <c r="B66" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1955,48 +2274,48 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>117</v>
+      <c r="A2">
+        <v>16</v>
       </c>
       <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2">
         <v>5488</v>
       </c>
-      <c r="C2">
+      <c r="G2">
         <v>3084</v>
-      </c>
-      <c r="D2">
-        <v>16</v>
-      </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2006,56 +2325,62 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:13" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+        <v>54</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E2">
         <v>-29.03668837129205</v>
@@ -2078,19 +2403,25 @@
       <c r="K2">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E3">
         <v>13.08056937520336</v>
@@ -2113,19 +2444,25 @@
       <c r="K3">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E4">
         <v>20.60276149624734</v>
@@ -2148,19 +2485,25 @@
       <c r="K4">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E5">
         <v>11.43099922005418</v>
@@ -2183,19 +2526,25 @@
       <c r="K5">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E6">
         <v>14.52182560559675</v>
@@ -2218,19 +2567,25 @@
       <c r="K6">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="C7" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E7">
         <v>7.603404674660883</v>
@@ -2253,19 +2608,25 @@
       <c r="K7">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E8">
         <v>-1.815703959053951</v>
@@ -2288,19 +2649,25 @@
       <c r="K8">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="C9" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E9">
         <v>6.347878895134601</v>
@@ -2323,19 +2690,25 @@
       <c r="K9">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E10">
         <v>-24.7921152876593</v>
@@ -2358,19 +2731,25 @@
       <c r="K10">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E11">
         <v>-0.2726434558319107</v>
@@ -2393,19 +2772,25 @@
       <c r="K11">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C12" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E12">
         <v>-40.40482862456627</v>
@@ -2428,19 +2813,25 @@
       <c r="K12">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E13">
         <v>10.45489006361177</v>
@@ -2463,19 +2854,25 @@
       <c r="K13">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E14">
         <v>-1.132590706856068</v>
@@ -2498,19 +2895,25 @@
       <c r="K14">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D15" t="s">
         <v>148</v>
-      </c>
-      <c r="D15" t="s">
-        <v>121</v>
       </c>
       <c r="E15">
         <v>20.46158158979754</v>
@@ -2533,19 +2936,25 @@
       <c r="K15">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E16">
         <v>3.289723066035493</v>
@@ -2568,19 +2977,25 @@
       <c r="K16">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B17" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" t="s">
         <v>151</v>
-      </c>
-      <c r="C17" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" t="s">
-        <v>124</v>
       </c>
       <c r="E17">
         <v>-10.33906358108227</v>
@@ -2603,19 +3018,25 @@
       <c r="K17">
         <v>0.8472</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E18">
         <v>-3.199725992983305</v>
@@ -2638,19 +3059,25 @@
       <c r="K18">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E19">
         <v>-18.30102171593667</v>
@@ -2673,19 +3100,25 @@
       <c r="K19">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
+        <v>180</v>
+      </c>
+      <c r="B20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" t="s">
         <v>153</v>
       </c>
-      <c r="B20" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" t="s">
-        <v>126</v>
-      </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E20">
         <v>-12.35518630816837</v>
@@ -2708,19 +3141,25 @@
       <c r="K20">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B21" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E21">
         <v>-5.98885249352225</v>
@@ -2743,19 +3182,25 @@
       <c r="K21">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B22" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E22">
         <v>31.62719350495113</v>
@@ -2778,19 +3223,25 @@
       <c r="K22">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B23" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" t="s">
         <v>159</v>
       </c>
-      <c r="C23" t="s">
-        <v>132</v>
-      </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E23">
         <v>3.109524346521162</v>
@@ -2813,19 +3264,25 @@
       <c r="K23">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B24" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E24">
         <v>-18.5075133674658</v>
@@ -2848,19 +3305,25 @@
       <c r="K24">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B25" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E25">
         <v>-8.841103606115809</v>
@@ -2883,19 +3346,25 @@
       <c r="K25">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E26">
         <v>19.44216629968949</v>
@@ -2918,19 +3387,25 @@
       <c r="K26">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B27" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E27">
         <v>-3.221146978052823</v>
@@ -2953,19 +3428,25 @@
       <c r="K27">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="C28" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="D28" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E28">
         <v>-14.42742049074879</v>
@@ -2988,19 +3469,25 @@
       <c r="K28">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E29">
         <v>8.887449114901896</v>
@@ -3023,19 +3510,25 @@
       <c r="K29">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B30" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="C30" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E30">
         <v>-16.79140477818959</v>
@@ -3058,19 +3551,25 @@
       <c r="K30">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="C31" t="s">
+        <v>175</v>
+      </c>
+      <c r="D31" t="s">
         <v>148</v>
-      </c>
-      <c r="D31" t="s">
-        <v>121</v>
       </c>
       <c r="E31">
         <v>63.75873513528938</v>
@@ -3093,19 +3592,25 @@
       <c r="K31">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B32" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E32">
         <v>-9.817522832852235</v>
@@ -3128,19 +3633,25 @@
       <c r="K32">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="C33" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="D33" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E33">
         <v>-15.37416983731738</v>
@@ -3163,19 +3674,25 @@
       <c r="K33">
         <v>0.2796</v>
       </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="D34" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E34">
         <v>-13.71325990712873</v>
@@ -3198,19 +3715,25 @@
       <c r="K34">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E35">
         <v>-4.835157290732149</v>
@@ -3233,19 +3756,25 @@
       <c r="K35">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E36">
         <v>8.539242593660607</v>
@@ -3268,19 +3797,25 @@
       <c r="K36">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B37" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E37">
         <v>-1.249855280976475</v>
@@ -3303,19 +3838,25 @@
       <c r="K37">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B38" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E38">
         <v>-23.4297593894653</v>
@@ -3338,19 +3879,25 @@
       <c r="K38">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E39">
         <v>6.999856436791639</v>
@@ -3373,19 +3920,25 @@
       <c r="K39">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E40">
         <v>-23.08582380590919</v>
@@ -3408,19 +3961,25 @@
       <c r="K40">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="D41" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E41">
         <v>-2.196901127944684</v>
@@ -3443,19 +4002,25 @@
       <c r="K41">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E42">
         <v>-3.759322107605664</v>
@@ -3478,19 +4043,25 @@
       <c r="K42">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="D43" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E43">
         <v>11.4734514780776</v>
@@ -3513,19 +4084,25 @@
       <c r="K43">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B44" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="C44" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="D44" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E44">
         <v>-12.95525034438228</v>
@@ -3548,19 +4125,25 @@
       <c r="K44">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B45" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="C45" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="D45" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E45">
         <v>-23.52364066028841</v>
@@ -3583,19 +4166,25 @@
       <c r="K45">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B46" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C46" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="D46" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E46">
         <v>5.06439977679006</v>
@@ -3618,19 +4207,25 @@
       <c r="K46">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B47" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="C47" t="s">
+        <v>175</v>
+      </c>
+      <c r="D47" t="s">
         <v>148</v>
-      </c>
-      <c r="D47" t="s">
-        <v>121</v>
       </c>
       <c r="E47">
         <v>74.73772560814433</v>
@@ -3653,19 +4248,25 @@
       <c r="K47">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B48" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C48" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="D48" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E48">
         <v>8.668031025307945</v>
@@ -3688,19 +4289,25 @@
       <c r="K48">
         <v>0.2933</v>
       </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B49" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C49" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="D49" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E49">
         <v>-6.733737004339182</v>
@@ -3722,6 +4329,12 @@
       </c>
       <c r="K49">
         <v>0.2933</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3731,558 +4344,540 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1">
+    <row r="1" spans="1:13" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>74</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B2" t="s">
-        <v>121</v>
+        <v>214</v>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" t="s">
-        <v>189</v>
+        <v>148</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>2059</v>
+        <v>15.61894001581623</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>4.961406254252276</v>
       </c>
       <c r="G2">
-        <v>122</v>
+        <v>27.35861463212197</v>
       </c>
       <c r="H2">
+        <v>0.009360992809377048</v>
+      </c>
+      <c r="I2">
+        <v>36.40192704096297</v>
+      </c>
+      <c r="J2">
+        <v>0.001713171134239212</v>
+      </c>
+      <c r="K2" t="s">
+        <v>215</v>
+      </c>
+      <c r="L2" t="s">
+        <v>216</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>-15.23657874635845</v>
+      </c>
+      <c r="F3">
+        <v>-27.33697262798194</v>
+      </c>
+      <c r="G3">
+        <v>-1.121136257679334</v>
+      </c>
+      <c r="H3">
+        <v>0.03879363363538978</v>
+      </c>
+      <c r="I3">
+        <v>36.40192704096297</v>
+      </c>
+      <c r="J3">
+        <v>0.001713171134239212</v>
+      </c>
+      <c r="K3" t="s">
+        <v>215</v>
+      </c>
+      <c r="L3" t="s">
+        <v>216</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>11.45389485956478</v>
+      </c>
+      <c r="F4">
+        <v>8.434385401768839</v>
+      </c>
+      <c r="G4">
+        <v>14.55748684645828</v>
+      </c>
+      <c r="H4">
+        <v>3.358742104888466E-05</v>
+      </c>
+      <c r="I4">
+        <v>7.785141361612591</v>
+      </c>
+      <c r="J4">
+        <v>0.01023059163043604</v>
+      </c>
+      <c r="K4" t="s">
+        <v>215</v>
+      </c>
+      <c r="L4" t="s">
+        <v>218</v>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>3.403765539114278</v>
+      </c>
+      <c r="F5">
+        <v>-1.652146367364871</v>
+      </c>
+      <c r="G5">
+        <v>8.719594101238638</v>
+      </c>
+      <c r="H5">
+        <v>0.1583886847272819</v>
+      </c>
+      <c r="I5">
+        <v>7.785141361612591</v>
+      </c>
+      <c r="J5">
+        <v>0.01023059163043604</v>
+      </c>
+      <c r="K5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L5" t="s">
+        <v>218</v>
+      </c>
+      <c r="M5" t="b">
         <v>0</v>
       </c>
-      <c r="I2">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E3">
-        <v>2059</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>34</v>
-      </c>
-      <c r="H3">
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" t="b">
         <v>0</v>
       </c>
-      <c r="I3">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D4" t="s">
-        <v>189</v>
-      </c>
-      <c r="E4">
-        <v>2059</v>
-      </c>
-      <c r="F4">
-        <v>48</v>
-      </c>
-      <c r="G4">
-        <v>196</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5">
-        <v>2059</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
+      <c r="C6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>15.87143976683438</v>
+      </c>
+      <c r="F6">
+        <v>5.790070954985849</v>
+      </c>
+      <c r="G6">
+        <v>26.91352253040866</v>
+      </c>
+      <c r="H6">
+        <v>0.0064844785031514</v>
+      </c>
+      <c r="I6">
+        <v>42.9036681543794</v>
+      </c>
+      <c r="J6">
+        <v>0.002763676599144667</v>
+      </c>
+      <c r="K6" t="s">
+        <v>220</v>
+      </c>
+      <c r="L6" t="s">
+        <v>221</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>-18.9163992336026</v>
+      </c>
+      <c r="F7">
+        <v>-33.18007325802282</v>
+      </c>
+      <c r="G7">
+        <v>-1.607938921694463</v>
+      </c>
+      <c r="H7">
+        <v>0.0374019796115013</v>
+      </c>
+      <c r="I7">
+        <v>42.9036681543794</v>
+      </c>
+      <c r="J7">
+        <v>0.002763676599144667</v>
+      </c>
+      <c r="K7" t="s">
+        <v>220</v>
+      </c>
+      <c r="L7" t="s">
+        <v>221</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>17.31657252276526</v>
+      </c>
+      <c r="F8">
+        <v>8.525728406553789</v>
+      </c>
+      <c r="G8">
+        <v>26.81949608235106</v>
+      </c>
+      <c r="H8">
+        <v>0.001859499885412957</v>
+      </c>
+      <c r="I8">
+        <v>36.44598736038738</v>
+      </c>
+      <c r="J8">
+        <v>0.00100838258081328</v>
+      </c>
+      <c r="K8" t="s">
+        <v>220</v>
+      </c>
+      <c r="L8" t="s">
+        <v>223</v>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>-14.01977090546213</v>
+      </c>
+      <c r="F9">
+        <v>-25.61401399327416</v>
+      </c>
+      <c r="G9">
+        <v>-0.6183799932316214</v>
+      </c>
+      <c r="H9">
+        <v>0.04309196724158125</v>
+      </c>
+      <c r="I9">
+        <v>36.44598736038738</v>
+      </c>
+      <c r="J9">
+        <v>0.00100838258081328</v>
+      </c>
+      <c r="K9" t="s">
+        <v>220</v>
+      </c>
+      <c r="L9" t="s">
+        <v>223</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>33.55753247606519</v>
+      </c>
+      <c r="F10">
+        <v>8.805548736578551</v>
+      </c>
+      <c r="G10">
+        <v>63.94030165024578</v>
+      </c>
+      <c r="H10">
+        <v>0.01245017613942718</v>
+      </c>
+      <c r="I10">
+        <v>2.311450386423686</v>
+      </c>
+      <c r="J10">
+        <v>0.8464533285112503</v>
+      </c>
+      <c r="K10" t="s">
+        <v>220</v>
+      </c>
+      <c r="L10" t="s">
+        <v>225</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>30.54016141069946</v>
+      </c>
+      <c r="F11">
+        <v>8.862306914479291</v>
+      </c>
+      <c r="G11">
+        <v>56.53474764702933</v>
+      </c>
+      <c r="H11">
+        <v>0.01040156071818931</v>
+      </c>
+      <c r="I11">
+        <v>2.311450386423686</v>
+      </c>
+      <c r="J11">
+        <v>0.8464533285112503</v>
+      </c>
+      <c r="K11" t="s">
+        <v>220</v>
+      </c>
+      <c r="L11" t="s">
+        <v>225</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12">
         <v>7</v>
       </c>
-      <c r="H5">
+      <c r="E12">
+        <v>17.30682799899768</v>
+      </c>
+      <c r="F12">
+        <v>9.024840506994437</v>
+      </c>
+      <c r="G12">
+        <v>26.21795025055418</v>
+      </c>
+      <c r="H12">
+        <v>0.001770403301165119</v>
+      </c>
+      <c r="I12">
+        <v>3.809567648306289</v>
+      </c>
+      <c r="J12">
+        <v>0.4262518511068021</v>
+      </c>
+      <c r="K12" t="s">
+        <v>220</v>
+      </c>
+      <c r="L12" t="s">
+        <v>227</v>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B13" t="b">
         <v>0</v>
       </c>
-      <c r="I5">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" t="s">
-        <v>189</v>
-      </c>
-      <c r="E6">
-        <v>2059</v>
-      </c>
-      <c r="F6">
-        <v>54</v>
-      </c>
-      <c r="G6">
-        <v>106</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E7">
-        <v>2059</v>
-      </c>
-      <c r="F7">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>49</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E8">
-        <v>2059</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>32</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9">
-        <v>2059</v>
-      </c>
-      <c r="F9">
-        <v>65</v>
-      </c>
-      <c r="G9">
-        <v>172</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" t="s">
-        <v>170</v>
-      </c>
-      <c r="C10" t="s">
-        <v>196</v>
-      </c>
-      <c r="D10" t="s">
-        <v>189</v>
-      </c>
-      <c r="E10">
-        <v>2059</v>
-      </c>
-      <c r="F10">
-        <v>33</v>
-      </c>
-      <c r="G10">
-        <v>73</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E11">
-        <v>2059</v>
-      </c>
-      <c r="F11">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>51</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>195</v>
-      </c>
-      <c r="B12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D12" t="s">
-        <v>189</v>
-      </c>
-      <c r="E12">
-        <v>2059</v>
-      </c>
-      <c r="F12">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>48</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>195</v>
-      </c>
-      <c r="B13" t="s">
-        <v>118</v>
-      </c>
       <c r="C13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" t="s">
-        <v>190</v>
+        <v>151</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>2059</v>
+        <v>13.00194255352107</v>
       </c>
       <c r="F13">
-        <v>13</v>
+        <v>4.199400288768951</v>
       </c>
       <c r="G13">
-        <v>38</v>
+        <v>22.54810474418463</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.009169630429916541</v>
       </c>
       <c r="I13">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>195</v>
-      </c>
-      <c r="B14" t="s">
-        <v>153</v>
-      </c>
-      <c r="C14" t="s">
-        <v>198</v>
-      </c>
-      <c r="D14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E14">
-        <v>2059</v>
-      </c>
-      <c r="F14">
-        <v>17</v>
-      </c>
-      <c r="G14">
-        <v>31</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>195</v>
-      </c>
-      <c r="B15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" t="s">
-        <v>190</v>
-      </c>
-      <c r="E15">
-        <v>2059</v>
-      </c>
-      <c r="F15">
-        <v>39</v>
-      </c>
-      <c r="G15">
-        <v>110</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>199</v>
-      </c>
-      <c r="B16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C16" t="s">
-        <v>200</v>
-      </c>
-      <c r="D16" t="s">
-        <v>189</v>
-      </c>
-      <c r="E16">
-        <v>2059</v>
-      </c>
-      <c r="F16">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>100</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>199</v>
-      </c>
-      <c r="B17" t="s">
-        <v>192</v>
-      </c>
-      <c r="C17" t="s">
-        <v>200</v>
-      </c>
-      <c r="D17" t="s">
-        <v>190</v>
-      </c>
-      <c r="E17">
-        <v>2059</v>
-      </c>
-      <c r="F17">
-        <v>16</v>
-      </c>
-      <c r="G17">
-        <v>19</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>199</v>
-      </c>
-      <c r="B18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C18" t="s">
-        <v>201</v>
-      </c>
-      <c r="D18" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18">
-        <v>2059</v>
-      </c>
-      <c r="F18">
-        <v>7</v>
-      </c>
-      <c r="G18">
-        <v>13</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>51.475</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>199</v>
-      </c>
-      <c r="B19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C19" t="s">
-        <v>201</v>
-      </c>
-      <c r="D19" t="s">
-        <v>190</v>
-      </c>
-      <c r="E19">
-        <v>2059</v>
-      </c>
-      <c r="F19">
-        <v>33</v>
-      </c>
-      <c r="G19">
-        <v>55</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>51.475</v>
+        <v>3.809567648306289</v>
+      </c>
+      <c r="J13">
+        <v>0.4262518511068021</v>
+      </c>
+      <c r="K13" t="s">
+        <v>220</v>
+      </c>
+      <c r="L13" t="s">
+        <v>227</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4292,884 +4887,558 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1">
+    <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>229</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E2" t="s">
-        <v>190</v>
+        <v>230</v>
+      </c>
+      <c r="E2">
+        <v>2059</v>
       </c>
       <c r="F2">
+        <v>24</v>
+      </c>
+      <c r="G2">
+        <v>122</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E3">
+        <v>2059</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>34</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E4">
+        <v>2059</v>
+      </c>
+      <c r="F4">
+        <v>48</v>
+      </c>
+      <c r="G4">
+        <v>196</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" t="s">
+        <v>231</v>
+      </c>
+      <c r="E5">
+        <v>2059</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E6">
+        <v>2059</v>
+      </c>
+      <c r="F6">
+        <v>54</v>
+      </c>
+      <c r="G6">
+        <v>106</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7">
+        <v>2059</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
         <v>49</v>
       </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I2" t="s">
-        <v>194</v>
-      </c>
-      <c r="J2" t="s">
-        <v>190</v>
-      </c>
-      <c r="K2">
-        <v>0.02811640096906698</v>
-      </c>
-      <c r="L2">
-        <v>0.1124656038762679</v>
-      </c>
-      <c r="M2" t="s">
-        <v>203</v>
-      </c>
-      <c r="N2">
-        <v>-0.7258399112794024</v>
-      </c>
-      <c r="O2">
-        <v>-0.1551216800512224</v>
-      </c>
-      <c r="P2">
-        <v>0.7755102040816326</v>
-      </c>
-      <c r="Q2">
-        <v>-1.551040271821073</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F3">
-        <v>106</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>193</v>
-      </c>
-      <c r="I3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J3" t="s">
-        <v>189</v>
-      </c>
-      <c r="K3">
-        <v>0.3083645129446252</v>
-      </c>
-      <c r="L3">
-        <v>0.4111526839261669</v>
-      </c>
-      <c r="M3" t="s">
-        <v>204</v>
-      </c>
-      <c r="N3">
-        <v>0.918071182257265</v>
-      </c>
-      <c r="O3">
-        <v>0.2784657250072696</v>
-      </c>
-      <c r="P3">
-        <v>0.6320754716981132</v>
-      </c>
-      <c r="Q3">
-        <v>0.5109356070124644</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
-      <c r="A4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F4">
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" t="s">
+        <v>230</v>
+      </c>
+      <c r="E8">
+        <v>2059</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>32</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E9">
+        <v>2059</v>
+      </c>
+      <c r="F9">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>172</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D10" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10">
+        <v>2059</v>
+      </c>
+      <c r="F10">
+        <v>33</v>
+      </c>
+      <c r="G10">
+        <v>73</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11">
+        <v>2059</v>
+      </c>
+      <c r="F11">
+        <v>14</v>
+      </c>
+      <c r="G11">
+        <v>51</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" t="s">
+        <v>238</v>
+      </c>
+      <c r="D12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E12">
+        <v>2059</v>
+      </c>
+      <c r="F12">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>48</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>236</v>
+      </c>
+      <c r="B13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D13" t="s">
+        <v>231</v>
+      </c>
+      <c r="E13">
+        <v>2059</v>
+      </c>
+      <c r="F13">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>38</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" t="s">
+        <v>239</v>
+      </c>
+      <c r="D14" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14">
+        <v>2059</v>
+      </c>
+      <c r="F14">
+        <v>17</v>
+      </c>
+      <c r="G14">
+        <v>31</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15">
+        <v>2059</v>
+      </c>
+      <c r="F15">
+        <v>39</v>
+      </c>
+      <c r="G15">
+        <v>110</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D16" t="s">
+        <v>230</v>
+      </c>
+      <c r="E16">
+        <v>2059</v>
+      </c>
+      <c r="F16">
+        <v>66</v>
+      </c>
+      <c r="G16">
+        <v>100</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" t="s">
+        <v>233</v>
+      </c>
+      <c r="C17" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" t="s">
+        <v>231</v>
+      </c>
+      <c r="E17">
+        <v>2059</v>
+      </c>
+      <c r="F17">
         <v>16</v>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I4" t="s">
-        <v>194</v>
-      </c>
-      <c r="J4" t="s">
-        <v>190</v>
-      </c>
-      <c r="K4">
-        <v>0.5166444797844136</v>
-      </c>
-      <c r="L4">
-        <v>0.5166444797844136</v>
-      </c>
-      <c r="M4" t="s">
-        <v>204</v>
-      </c>
-      <c r="N4">
-        <v>-1.273695086711304</v>
-      </c>
-      <c r="O4">
-        <v>-0.01097168334189445</v>
-      </c>
-      <c r="P4">
-        <v>0.625</v>
-      </c>
-      <c r="Q4">
-        <v>-0.2868082065766502</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" t="s">
-        <v>205</v>
-      </c>
-      <c r="E5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5">
-        <v>54</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>193</v>
-      </c>
-      <c r="I5" t="s">
-        <v>194</v>
-      </c>
-      <c r="J5" t="s">
-        <v>189</v>
-      </c>
-      <c r="K5">
-        <v>0.09989191141023498</v>
-      </c>
-      <c r="L5">
-        <v>0.19978382282047</v>
-      </c>
-      <c r="M5" t="s">
-        <v>204</v>
-      </c>
-      <c r="N5">
-        <v>1.283176345008311</v>
-      </c>
-      <c r="O5">
-        <v>0.51021220914251</v>
-      </c>
-      <c r="P5">
-        <v>0.7592592592592593</v>
-      </c>
-      <c r="Q5">
-        <v>1.000469676660108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F6">
-        <v>172</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>194</v>
-      </c>
-      <c r="I6" t="s">
-        <v>193</v>
-      </c>
-      <c r="J6" t="s">
-        <v>190</v>
-      </c>
-      <c r="K6">
-        <v>0.2056803019597374</v>
-      </c>
-      <c r="L6">
-        <v>0.2742404026129832</v>
-      </c>
-      <c r="M6" t="s">
-        <v>204</v>
-      </c>
-      <c r="N6">
-        <v>-0.6958096544338495</v>
-      </c>
-      <c r="O6">
-        <v>-0.1159811897425118</v>
-      </c>
-      <c r="P6">
-        <v>0.7034883720930233</v>
-      </c>
-      <c r="Q6">
-        <v>-0.6868072987759725</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" t="s">
-        <v>202</v>
-      </c>
-      <c r="E7" t="s">
-        <v>189</v>
-      </c>
-      <c r="F7">
-        <v>32</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>194</v>
-      </c>
-      <c r="I7" t="s">
-        <v>193</v>
-      </c>
-      <c r="J7" t="s">
-        <v>189</v>
-      </c>
-      <c r="K7">
-        <v>0.00205794964484609</v>
-      </c>
-      <c r="L7">
-        <v>0.004359555799575449</v>
-      </c>
-      <c r="M7" t="s">
-        <v>206</v>
-      </c>
-      <c r="N7">
-        <v>1.191621191349772</v>
-      </c>
-      <c r="O7">
-        <v>0.8086899578323585</v>
-      </c>
-      <c r="P7">
-        <v>0.875</v>
-      </c>
-      <c r="Q7">
-        <v>2.686565256023065</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E8" t="s">
-        <v>190</v>
-      </c>
-      <c r="F8">
-        <v>65</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>194</v>
-      </c>
-      <c r="I8" t="s">
-        <v>193</v>
-      </c>
-      <c r="J8" t="s">
-        <v>190</v>
-      </c>
-      <c r="K8">
-        <v>0.3170751160616128</v>
-      </c>
-      <c r="L8">
-        <v>0.3170751160616128</v>
-      </c>
-      <c r="M8" t="s">
-        <v>204</v>
-      </c>
-      <c r="N8">
-        <v>-0.973285952397791</v>
-      </c>
-      <c r="O8">
-        <v>-0.1301074378981521</v>
-      </c>
-      <c r="P8">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="Q8">
-        <v>-0.4988378399066278</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" t="s">
-        <v>205</v>
-      </c>
-      <c r="E9" t="s">
-        <v>189</v>
-      </c>
-      <c r="F9">
+      <c r="G17">
         <v>19</v>
       </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="s">
-        <v>194</v>
-      </c>
-      <c r="I9" t="s">
-        <v>193</v>
-      </c>
-      <c r="J9" t="s">
-        <v>189</v>
-      </c>
-      <c r="K9">
-        <v>0.002179777899787724</v>
-      </c>
-      <c r="L9">
-        <v>0.004359555799575449</v>
-      </c>
-      <c r="M9" t="s">
-        <v>206</v>
-      </c>
-      <c r="N9">
-        <v>1.716849938307574</v>
-      </c>
-      <c r="O9">
-        <v>1.109424334064693</v>
-      </c>
-      <c r="P9">
-        <v>0.8947368421052632</v>
-      </c>
-      <c r="Q9">
-        <v>2.661587754932326</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" t="s">
-        <v>202</v>
-      </c>
-      <c r="E10" t="s">
-        <v>190</v>
-      </c>
-      <c r="F10">
-        <v>34</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="s">
-        <v>188</v>
-      </c>
-      <c r="I10" t="s">
-        <v>191</v>
-      </c>
-      <c r="J10" t="s">
-        <v>190</v>
-      </c>
-      <c r="K10">
-        <v>0.3187619824129026</v>
-      </c>
-      <c r="L10">
-        <v>0.4250159765505368</v>
-      </c>
-      <c r="M10" t="s">
-        <v>204</v>
-      </c>
-      <c r="N10">
-        <v>-0.633023201706413</v>
-      </c>
-      <c r="O10">
-        <v>-0.09019867659319955</v>
-      </c>
-      <c r="P10">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="Q10">
-        <v>-0.4965334809172235</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" t="s">
-        <v>187</v>
-      </c>
-      <c r="B11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" t="s">
-        <v>189</v>
-      </c>
-      <c r="F11">
-        <v>122</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>188</v>
-      </c>
-      <c r="I11" t="s">
-        <v>191</v>
-      </c>
-      <c r="J11" t="s">
-        <v>189</v>
-      </c>
-      <c r="K11">
-        <v>0.000768366270010823</v>
-      </c>
-      <c r="L11">
-        <v>0.001536732540021646</v>
-      </c>
-      <c r="M11" t="s">
-        <v>206</v>
-      </c>
-      <c r="N11">
-        <v>0.5371813707305108</v>
-      </c>
-      <c r="O11">
-        <v>0.2950199217909802</v>
-      </c>
-      <c r="P11">
-        <v>0.9180327868852459</v>
-      </c>
-      <c r="Q11">
-        <v>3.114431708190481</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D12" t="s">
-        <v>205</v>
-      </c>
-      <c r="E12" t="s">
-        <v>190</v>
-      </c>
-      <c r="F12">
-        <v>14</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>188</v>
-      </c>
-      <c r="I12" t="s">
-        <v>191</v>
-      </c>
-      <c r="J12" t="s">
-        <v>190</v>
-      </c>
-      <c r="K12">
-        <v>0.5966613731568553</v>
-      </c>
-      <c r="L12">
-        <v>0.5966613731568553</v>
-      </c>
-      <c r="M12" t="s">
-        <v>204</v>
-      </c>
-      <c r="N12">
-        <v>-1.044533156972018</v>
-      </c>
-      <c r="O12">
-        <v>-0.1982404704985165</v>
-      </c>
-      <c r="P12">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="Q12">
-        <v>-0.224272076732449</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C13" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" t="s">
-        <v>205</v>
-      </c>
-      <c r="E13" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13">
-        <v>24</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>188</v>
-      </c>
-      <c r="I13" t="s">
-        <v>191</v>
-      </c>
-      <c r="J13" t="s">
-        <v>189</v>
-      </c>
-      <c r="K13">
-        <v>0.0005519921883541551</v>
-      </c>
-      <c r="L13">
-        <v>0.001536732540021646</v>
-      </c>
-      <c r="M13" t="s">
-        <v>206</v>
-      </c>
-      <c r="N13">
-        <v>0.7737914310005581</v>
-      </c>
-      <c r="O13">
-        <v>0.4023095300919867</v>
-      </c>
-      <c r="P13">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="Q13">
-        <v>3.258067068246689</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" t="s">
-        <v>190</v>
-      </c>
-      <c r="F14">
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" t="s">
+        <v>242</v>
+      </c>
+      <c r="D18" t="s">
+        <v>230</v>
+      </c>
+      <c r="E18">
+        <v>2059</v>
+      </c>
+      <c r="F18">
         <v>7</v>
       </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>191</v>
-      </c>
-      <c r="I14" t="s">
-        <v>188</v>
-      </c>
-      <c r="J14" t="s">
-        <v>190</v>
-      </c>
-      <c r="K14">
-        <v>0.7391088073972578</v>
-      </c>
-      <c r="L14">
-        <v>0.7391088073972578</v>
-      </c>
-      <c r="M14" t="s">
-        <v>204</v>
-      </c>
-      <c r="N14">
-        <v>-0.7111835336781603</v>
-      </c>
-      <c r="O14">
-        <v>-0.01369609822375014</v>
-      </c>
-      <c r="P14">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="Q14">
-        <v>-0.1312916225337498</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15" t="s">
-        <v>187</v>
-      </c>
-      <c r="B15" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" t="s">
-        <v>202</v>
-      </c>
-      <c r="E15" t="s">
-        <v>189</v>
-      </c>
-      <c r="F15">
-        <v>196</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>191</v>
-      </c>
-      <c r="I15" t="s">
-        <v>188</v>
-      </c>
-      <c r="J15" t="s">
-        <v>189</v>
-      </c>
-      <c r="K15">
-        <v>0.0151472518236927</v>
-      </c>
-      <c r="L15">
-        <v>0.02272087773553904</v>
-      </c>
-      <c r="M15" t="s">
-        <v>206</v>
-      </c>
-      <c r="N15">
-        <v>0.574688710741055</v>
-      </c>
-      <c r="O15">
-        <v>0.1744719349694764</v>
-      </c>
-      <c r="P15">
-        <v>0.7448979591836735</v>
-      </c>
-      <c r="Q15">
-        <v>1.819666154360976</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" t="s">
-        <v>205</v>
-      </c>
-      <c r="E16" t="s">
-        <v>190</v>
-      </c>
-      <c r="F16">
-        <v>3</v>
-      </c>
-      <c r="G16" t="b">
+      <c r="G18">
+        <v>13</v>
+      </c>
+      <c r="H18">
         <v>0</v>
       </c>
-      <c r="H16" t="s">
-        <v>191</v>
-      </c>
-      <c r="M16" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" t="s">
-        <v>187</v>
-      </c>
-      <c r="B17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" t="s">
-        <v>205</v>
-      </c>
-      <c r="E17" t="s">
-        <v>189</v>
-      </c>
-      <c r="F17">
-        <v>48</v>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="s">
-        <v>191</v>
-      </c>
-      <c r="I17" t="s">
-        <v>188</v>
-      </c>
-      <c r="J17" t="s">
-        <v>189</v>
-      </c>
-      <c r="K17">
-        <v>0.005320244326701801</v>
-      </c>
-      <c r="L17">
-        <v>0.0159607329801054</v>
-      </c>
-      <c r="M17" t="s">
-        <v>206</v>
-      </c>
-      <c r="N17">
-        <v>0.8503634914478839</v>
-      </c>
-      <c r="O17">
-        <v>0.238967985783441</v>
-      </c>
-      <c r="P17">
-        <v>0.75</v>
-      </c>
-      <c r="Q17">
-        <v>2.274068422723402</v>
+      <c r="I18">
+        <v>51.475</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B19" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" t="s">
+        <v>242</v>
+      </c>
+      <c r="D19" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19">
+        <v>2059</v>
+      </c>
+      <c r="F19">
+        <v>33</v>
+      </c>
+      <c r="G19">
+        <v>55</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>51.475</v>
       </c>
     </row>
   </sheetData>
@@ -5179,40 +5448,887 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1">
+    <row r="1" spans="1:17" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="F1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>151</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F2">
+        <v>49</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I2" t="s">
+        <v>235</v>
+      </c>
+      <c r="J2" t="s">
+        <v>231</v>
+      </c>
+      <c r="K2">
+        <v>0.02811640096906698</v>
+      </c>
+      <c r="L2">
+        <v>0.1124656038762679</v>
+      </c>
+      <c r="M2" t="s">
+        <v>244</v>
+      </c>
+      <c r="N2">
+        <v>-0.7258399112794024</v>
+      </c>
+      <c r="O2">
+        <v>-0.1551216800512224</v>
+      </c>
+      <c r="P2">
+        <v>0.7755102040816326</v>
+      </c>
+      <c r="Q2">
+        <v>-1.551040271821073</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="C3" t="s">
-        <v>211</v>
+        <v>151</v>
+      </c>
+      <c r="D3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3">
+        <v>106</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J3" t="s">
+        <v>230</v>
+      </c>
+      <c r="K3">
+        <v>0.3083645129446252</v>
+      </c>
+      <c r="L3">
+        <v>0.4111526839261669</v>
+      </c>
+      <c r="M3" t="s">
+        <v>245</v>
+      </c>
+      <c r="N3">
+        <v>0.918071182257265</v>
+      </c>
+      <c r="O3">
+        <v>0.2784657250072696</v>
+      </c>
+      <c r="P3">
+        <v>0.6320754716981132</v>
+      </c>
+      <c r="Q3">
+        <v>0.5109356070124644</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F4">
+        <v>16</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I4" t="s">
+        <v>235</v>
+      </c>
+      <c r="J4" t="s">
+        <v>231</v>
+      </c>
+      <c r="K4">
+        <v>0.5166444797844136</v>
+      </c>
+      <c r="L4">
+        <v>0.5166444797844136</v>
+      </c>
+      <c r="M4" t="s">
+        <v>245</v>
+      </c>
+      <c r="N4">
+        <v>-1.273695086711304</v>
+      </c>
+      <c r="O4">
+        <v>-0.01097168334189445</v>
+      </c>
+      <c r="P4">
+        <v>0.625</v>
+      </c>
+      <c r="Q4">
+        <v>-0.2868082065766502</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F5">
+        <v>54</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>234</v>
+      </c>
+      <c r="I5" t="s">
+        <v>235</v>
+      </c>
+      <c r="J5" t="s">
+        <v>230</v>
+      </c>
+      <c r="K5">
+        <v>0.09989191141023498</v>
+      </c>
+      <c r="L5">
+        <v>0.19978382282047</v>
+      </c>
+      <c r="M5" t="s">
+        <v>245</v>
+      </c>
+      <c r="N5">
+        <v>1.283176345008311</v>
+      </c>
+      <c r="O5">
+        <v>0.51021220914251</v>
+      </c>
+      <c r="P5">
+        <v>0.7592592592592593</v>
+      </c>
+      <c r="Q5">
+        <v>1.000469676660108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F6">
+        <v>172</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>235</v>
+      </c>
+      <c r="I6" t="s">
+        <v>234</v>
+      </c>
+      <c r="J6" t="s">
+        <v>231</v>
+      </c>
+      <c r="K6">
+        <v>0.2056803019597374</v>
+      </c>
+      <c r="L6">
+        <v>0.2742404026129832</v>
+      </c>
+      <c r="M6" t="s">
+        <v>245</v>
+      </c>
+      <c r="N6">
+        <v>-0.6958096544338495</v>
+      </c>
+      <c r="O6">
+        <v>-0.1159811897425118</v>
+      </c>
+      <c r="P6">
+        <v>0.7034883720930233</v>
+      </c>
+      <c r="Q6">
+        <v>-0.6868072987759725</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E7" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7">
+        <v>32</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>235</v>
+      </c>
+      <c r="I7" t="s">
+        <v>234</v>
+      </c>
+      <c r="J7" t="s">
+        <v>230</v>
+      </c>
+      <c r="K7">
+        <v>0.00205794964484609</v>
+      </c>
+      <c r="L7">
+        <v>0.004359555799575449</v>
+      </c>
+      <c r="M7" t="s">
+        <v>247</v>
+      </c>
+      <c r="N7">
+        <v>1.191621191349772</v>
+      </c>
+      <c r="O7">
+        <v>0.8086899578323585</v>
+      </c>
+      <c r="P7">
+        <v>0.875</v>
+      </c>
+      <c r="Q7">
+        <v>2.686565256023065</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" t="s">
+        <v>231</v>
+      </c>
+      <c r="F8">
+        <v>65</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>235</v>
+      </c>
+      <c r="I8" t="s">
+        <v>234</v>
+      </c>
+      <c r="J8" t="s">
+        <v>231</v>
+      </c>
+      <c r="K8">
+        <v>0.3170751160616128</v>
+      </c>
+      <c r="L8">
+        <v>0.3170751160616128</v>
+      </c>
+      <c r="M8" t="s">
+        <v>245</v>
+      </c>
+      <c r="N8">
+        <v>-0.973285952397791</v>
+      </c>
+      <c r="O8">
+        <v>-0.1301074378981521</v>
+      </c>
+      <c r="P8">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="Q8">
+        <v>-0.4988378399066278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E9" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9">
+        <v>19</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>235</v>
+      </c>
+      <c r="I9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J9" t="s">
+        <v>230</v>
+      </c>
+      <c r="K9">
+        <v>0.002179777899787724</v>
+      </c>
+      <c r="L9">
+        <v>0.004359555799575449</v>
+      </c>
+      <c r="M9" t="s">
+        <v>247</v>
+      </c>
+      <c r="N9">
+        <v>1.716849938307574</v>
+      </c>
+      <c r="O9">
+        <v>1.109424334064693</v>
+      </c>
+      <c r="P9">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="Q9">
+        <v>2.661587754932326</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" t="s">
+        <v>243</v>
+      </c>
+      <c r="E10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10">
+        <v>34</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>229</v>
+      </c>
+      <c r="I10" t="s">
+        <v>232</v>
+      </c>
+      <c r="J10" t="s">
+        <v>231</v>
+      </c>
+      <c r="K10">
+        <v>0.3187619824129026</v>
+      </c>
+      <c r="L10">
+        <v>0.4250159765505368</v>
+      </c>
+      <c r="M10" t="s">
+        <v>245</v>
+      </c>
+      <c r="N10">
+        <v>-0.633023201706413</v>
+      </c>
+      <c r="O10">
+        <v>-0.09019867659319955</v>
+      </c>
+      <c r="P10">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="Q10">
+        <v>-0.4965334809172235</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" t="s">
+        <v>243</v>
+      </c>
+      <c r="E11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F11">
+        <v>122</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>229</v>
+      </c>
+      <c r="I11" t="s">
+        <v>232</v>
+      </c>
+      <c r="J11" t="s">
+        <v>230</v>
+      </c>
+      <c r="K11">
+        <v>0.000768366270010823</v>
+      </c>
+      <c r="L11">
+        <v>0.001536732540021646</v>
+      </c>
+      <c r="M11" t="s">
+        <v>247</v>
+      </c>
+      <c r="N11">
+        <v>0.5371813707305108</v>
+      </c>
+      <c r="O11">
+        <v>0.2950199217909802</v>
+      </c>
+      <c r="P11">
+        <v>0.9180327868852459</v>
+      </c>
+      <c r="Q11">
+        <v>3.114431708190481</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" t="s">
+        <v>246</v>
+      </c>
+      <c r="E12" t="s">
+        <v>231</v>
+      </c>
+      <c r="F12">
+        <v>14</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>229</v>
+      </c>
+      <c r="I12" t="s">
+        <v>232</v>
+      </c>
+      <c r="J12" t="s">
+        <v>231</v>
+      </c>
+      <c r="K12">
+        <v>0.5966613731568553</v>
+      </c>
+      <c r="L12">
+        <v>0.5966613731568553</v>
+      </c>
+      <c r="M12" t="s">
+        <v>245</v>
+      </c>
+      <c r="N12">
+        <v>-1.044533156972018</v>
+      </c>
+      <c r="O12">
+        <v>-0.1982404704985165</v>
+      </c>
+      <c r="P12">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="Q12">
+        <v>-0.224272076732449</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D13" t="s">
+        <v>246</v>
+      </c>
+      <c r="E13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F13">
+        <v>24</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>229</v>
+      </c>
+      <c r="I13" t="s">
+        <v>232</v>
+      </c>
+      <c r="J13" t="s">
+        <v>230</v>
+      </c>
+      <c r="K13">
+        <v>0.0005519921883541551</v>
+      </c>
+      <c r="L13">
+        <v>0.001536732540021646</v>
+      </c>
+      <c r="M13" t="s">
+        <v>247</v>
+      </c>
+      <c r="N13">
+        <v>0.7737914310005581</v>
+      </c>
+      <c r="O13">
+        <v>0.4023095300919867</v>
+      </c>
+      <c r="P13">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="Q13">
+        <v>3.258067068246689</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" t="s">
+        <v>243</v>
+      </c>
+      <c r="E14" t="s">
+        <v>231</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>232</v>
+      </c>
+      <c r="I14" t="s">
+        <v>229</v>
+      </c>
+      <c r="J14" t="s">
+        <v>231</v>
+      </c>
+      <c r="K14">
+        <v>0.7391088073972578</v>
+      </c>
+      <c r="L14">
+        <v>0.7391088073972578</v>
+      </c>
+      <c r="M14" t="s">
+        <v>245</v>
+      </c>
+      <c r="N14">
+        <v>-0.7111835336781603</v>
+      </c>
+      <c r="O14">
+        <v>-0.01369609822375014</v>
+      </c>
+      <c r="P14">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Q14">
+        <v>-0.1312916225337498</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" t="s">
+        <v>243</v>
+      </c>
+      <c r="E15" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15">
+        <v>196</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>232</v>
+      </c>
+      <c r="I15" t="s">
+        <v>229</v>
+      </c>
+      <c r="J15" t="s">
+        <v>230</v>
+      </c>
+      <c r="K15">
+        <v>0.0151472518236927</v>
+      </c>
+      <c r="L15">
+        <v>0.02272087773553904</v>
+      </c>
+      <c r="M15" t="s">
+        <v>247</v>
+      </c>
+      <c r="N15">
+        <v>0.574688710741055</v>
+      </c>
+      <c r="O15">
+        <v>0.1744719349694764</v>
+      </c>
+      <c r="P15">
+        <v>0.7448979591836735</v>
+      </c>
+      <c r="Q15">
+        <v>1.819666154360976</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" t="s">
+        <v>246</v>
+      </c>
+      <c r="E16" t="s">
+        <v>231</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>232</v>
+      </c>
+      <c r="I16" t="s">
+        <v>229</v>
+      </c>
+      <c r="M16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" t="s">
+        <v>246</v>
+      </c>
+      <c r="E17" t="s">
+        <v>230</v>
+      </c>
+      <c r="F17">
+        <v>48</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>232</v>
+      </c>
+      <c r="I17" t="s">
+        <v>229</v>
+      </c>
+      <c r="J17" t="s">
+        <v>230</v>
+      </c>
+      <c r="K17">
+        <v>0.005320244326701801</v>
+      </c>
+      <c r="L17">
+        <v>0.0159607329801054</v>
+      </c>
+      <c r="M17" t="s">
+        <v>247</v>
+      </c>
+      <c r="N17">
+        <v>0.8503634914478839</v>
+      </c>
+      <c r="O17">
+        <v>0.238967985783441</v>
+      </c>
+      <c r="P17">
+        <v>0.75</v>
+      </c>
+      <c r="Q17">
+        <v>2.274068422723402</v>
       </c>
     </row>
   </sheetData>
@@ -5222,579 +6338,644 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="B2" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="C2" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>215</v>
+        <v>262</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="B4" t="s">
-        <v>218</v>
+        <v>265</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>219</v>
+        <v>266</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>267</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="C7" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="C8" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="C9" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>229</v>
+        <v>276</v>
       </c>
       <c r="B10" t="s">
-        <v>230</v>
+        <v>277</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>231</v>
+        <v>278</v>
       </c>
       <c r="B11" t="s">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="C11" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="B12" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="B13" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="C13" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="B14" t="s">
-        <v>238</v>
+        <v>285</v>
       </c>
       <c r="C14" t="s">
-        <v>239</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="B15" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="C15" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="B16" t="s">
-        <v>243</v>
+        <v>290</v>
       </c>
       <c r="C16" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>244</v>
+        <v>291</v>
       </c>
       <c r="B17" t="s">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="C17" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="B18" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="C18" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="B19" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="C19" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="C20" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>252</v>
+        <v>299</v>
       </c>
       <c r="B21" t="s">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="C21" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="B22" t="s">
-        <v>255</v>
+        <v>302</v>
       </c>
       <c r="C22" t="s">
-        <v>239</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="B23" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="C23" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>258</v>
+        <v>305</v>
       </c>
       <c r="B24" t="s">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="C24" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="B25" t="s">
+        <v>308</v>
+      </c>
+      <c r="C25" t="s">
         <v>261</v>
-      </c>
-      <c r="C25" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>262</v>
+        <v>309</v>
       </c>
       <c r="B26" t="s">
-        <v>263</v>
+        <v>310</v>
       </c>
       <c r="C26" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="B27" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="C27" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>266</v>
+        <v>313</v>
       </c>
       <c r="B28" t="s">
-        <v>267</v>
+        <v>314</v>
       </c>
       <c r="C28" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="B29" t="s">
-        <v>269</v>
+        <v>316</v>
       </c>
       <c r="C29" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>270</v>
+        <v>317</v>
       </c>
       <c r="B30" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="C30" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="C31" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="C32" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s">
-        <v>277</v>
+        <v>324</v>
       </c>
       <c r="C33" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s">
-        <v>279</v>
+        <v>326</v>
       </c>
       <c r="C34" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="C35" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="C36" t="s">
-        <v>239</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="C37" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="C38" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="C39" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>290</v>
+        <v>337</v>
       </c>
       <c r="B40" t="s">
-        <v>291</v>
+        <v>338</v>
       </c>
       <c r="C40" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="C41" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>294</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s">
-        <v>295</v>
+        <v>342</v>
       </c>
       <c r="C42" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>296</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="C43" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s">
+        <v>308</v>
+      </c>
+      <c r="C44" t="s">
         <v>261</v>
-      </c>
-      <c r="C44" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="C45" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s">
-        <v>301</v>
+        <v>348</v>
       </c>
       <c r="C46" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>302</v>
+        <v>349</v>
       </c>
       <c r="B47" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="C47" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>304</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s">
-        <v>305</v>
+        <v>352</v>
       </c>
       <c r="C48" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s">
-        <v>307</v>
+        <v>354</v>
       </c>
       <c r="C49" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s">
-        <v>309</v>
+        <v>356</v>
       </c>
       <c r="C50" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>310</v>
+        <v>357</v>
       </c>
       <c r="B51" t="s">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="C51" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>312</v>
+        <v>359</v>
       </c>
       <c r="B52" t="s">
-        <v>313</v>
+        <v>360</v>
       </c>
       <c r="C52" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/04_Figures/F1/c_data/F1.xlsx
+++ b/04_Figures/F1/c_data/F1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="363">
   <si>
     <t>sheet</t>
   </si>
@@ -878,6 +878,12 @@
   </si>
   <si>
     <t>4.0.3</t>
+  </si>
+  <si>
+    <t>ggrepel</t>
+  </si>
+  <si>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>ggtext</t>
@@ -6403,7 +6409,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -6557,18 +6563,18 @@
         <v>285</v>
       </c>
       <c r="C14" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>286</v>
+      </c>
+      <c r="B15" t="s">
         <v>287</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>288</v>
-      </c>
-      <c r="C15" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6645,7 +6651,7 @@
         <v>302</v>
       </c>
       <c r="C22" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6656,7 +6662,7 @@
         <v>304</v>
       </c>
       <c r="C23" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6799,7 +6805,7 @@
         <v>330</v>
       </c>
       <c r="C36" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6810,7 +6816,7 @@
         <v>332</v>
       </c>
       <c r="C37" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6884,7 +6890,7 @@
         <v>345</v>
       </c>
       <c r="B44" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="C44" t="s">
         <v>261</v>
@@ -6892,10 +6898,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="C45" t="s">
         <v>261</v>
@@ -6903,10 +6909,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s">
-        <v>348</v>
+        <v>275</v>
       </c>
       <c r="C46" t="s">
         <v>261</v>
@@ -6975,6 +6981,17 @@
         <v>360</v>
       </c>
       <c r="C52" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>361</v>
+      </c>
+      <c r="B53" t="s">
+        <v>362</v>
+      </c>
+      <c r="C53" t="s">
         <v>261</v>
       </c>
     </row>

--- a/04_Figures/F1/c_data/F1.xlsx
+++ b/04_Figures/F1/c_data/F1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="312">
   <si>
     <t>sheet</t>
   </si>
@@ -45,7 +45,7 @@
     <t>b_pca</t>
   </si>
   <si>
-    <t>Panel b: PC1 and PC2 per biopsy within each time point, with that time point's PERMANOVA, gap k and forced-split adjusted Rand index.</t>
+    <t>Panel b: PC1 and PC2 per person at T1 and for the training and acute changes, with each window's PERMANOVA for group, gap k and forced-split adjusted Rand index.</t>
   </si>
   <si>
     <t>c_trait_effects</t>
@@ -126,16 +126,10 @@
     <t>Height of the design image in pixels.</t>
   </si>
   <si>
-    <t>timepoint</t>
-  </si>
-  <si>
-    <t>T1 baseline, T2 after training, T3 after the acute bout at the end of training.</t>
-  </si>
-  <si>
-    <t>sample_id</t>
-  </si>
-  <si>
-    <t>One biopsy: person and time point, e.g. S03_T1.</t>
+    <t>window</t>
+  </si>
+  <si>
+    <t>A time point's levels (T1, T2, T3) or a change per person (Training T2 - T1, Acute T3 - T2).</t>
   </si>
   <si>
     <t>subject</t>
@@ -165,31 +159,31 @@
     <t>pc1_share</t>
   </si>
   <si>
-    <t>Share of variance on PC1 at that time point.</t>
+    <t>Share of variance on PC1 in that window.</t>
   </si>
   <si>
     <t>pc2_share</t>
   </si>
   <si>
-    <t>Share of variance on PC2 at that time point.</t>
+    <t>Share of variance on PC2 in that window.</t>
   </si>
   <si>
     <t>permanova_n</t>
   </si>
   <si>
-    <t>Biopsies in that time point's PERMANOVA.</t>
+    <t>People in that window's PERMANOVA.</t>
   </si>
   <si>
     <t>permanova_r2</t>
   </si>
   <si>
-    <t>Share of distance variation HR/LR explains at that time point (PERMANOVA R squared).</t>
+    <t>Share of distance variation HR/LR explains in that window (PERMANOVA R squared).</t>
   </si>
   <si>
     <t>permanova_p</t>
   </si>
   <si>
-    <t>PERMANOVA p for HR/LR at that time point.</t>
+    <t>PERMANOVA p for HR/LR in that window.</t>
   </si>
   <si>
     <t>k_gap</t>
@@ -327,9 +321,6 @@
     <t>Proteins expected at p &lt; 0.05 in one direction by chance: 2.5% of those tested.</t>
   </si>
   <si>
-    <t>window</t>
-  </si>
-  <si>
     <t>Window the set comes from: Training (T2 - T1) or Acute (T3 - T2).</t>
   </si>
   <si>
@@ -462,16 +453,31 @@
     <t>T1</t>
   </si>
   <si>
-    <t>S03_T1</t>
-  </si>
-  <si>
     <t>HR_S03</t>
   </si>
   <si>
     <t>HR</t>
   </si>
   <si>
-    <t>S04_T1</t>
+    <t>HR_S10</t>
+  </si>
+  <si>
+    <t>HR_S16</t>
+  </si>
+  <si>
+    <t>HR_S22</t>
+  </si>
+  <si>
+    <t>HR_S24</t>
+  </si>
+  <si>
+    <t>HR_S27</t>
+  </si>
+  <si>
+    <t>HR_S28</t>
+  </si>
+  <si>
+    <t>HR_S29</t>
   </si>
   <si>
     <t>LR_S04</t>
@@ -480,190 +486,31 @@
     <t>LR</t>
   </si>
   <si>
-    <t>S05_T1</t>
-  </si>
-  <si>
     <t>LR_S05</t>
   </si>
   <si>
-    <t>S06_T1</t>
-  </si>
-  <si>
     <t>LR_S06</t>
   </si>
   <si>
-    <t>S10_T1</t>
-  </si>
-  <si>
-    <t>HR_S10</t>
-  </si>
-  <si>
-    <t>S12_T1</t>
-  </si>
-  <si>
     <t>LR_S12</t>
   </si>
   <si>
-    <t>S14_T1</t>
-  </si>
-  <si>
     <t>LR_S14</t>
   </si>
   <si>
-    <t>S16_T1</t>
-  </si>
-  <si>
-    <t>HR_S16</t>
-  </si>
-  <si>
-    <t>S17_T1</t>
-  </si>
-  <si>
     <t>LR_S17</t>
   </si>
   <si>
-    <t>S21_T1</t>
-  </si>
-  <si>
     <t>LR_S21</t>
   </si>
   <si>
-    <t>S22_T1</t>
-  </si>
-  <si>
-    <t>HR_S22</t>
-  </si>
-  <si>
-    <t>S24_T1</t>
-  </si>
-  <si>
-    <t>HR_S24</t>
-  </si>
-  <si>
-    <t>S27_T1</t>
-  </si>
-  <si>
-    <t>HR_S27</t>
-  </si>
-  <si>
-    <t>S28_T1</t>
-  </si>
-  <si>
-    <t>HR_S28</t>
-  </si>
-  <si>
-    <t>S29_T1</t>
-  </si>
-  <si>
-    <t>HR_S29</t>
-  </si>
-  <si>
-    <t>S30_T1</t>
-  </si>
-  <si>
     <t>LR_S30</t>
   </si>
   <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>S03_T2</t>
-  </si>
-  <si>
-    <t>S04_T2</t>
-  </si>
-  <si>
-    <t>S05_T2</t>
-  </si>
-  <si>
-    <t>S06_T2</t>
-  </si>
-  <si>
-    <t>S10_T2</t>
-  </si>
-  <si>
-    <t>S12_T2</t>
-  </si>
-  <si>
-    <t>S14_T2</t>
-  </si>
-  <si>
-    <t>S16_T2</t>
-  </si>
-  <si>
-    <t>S17_T2</t>
-  </si>
-  <si>
-    <t>S21_T2</t>
-  </si>
-  <si>
-    <t>S22_T2</t>
-  </si>
-  <si>
-    <t>S24_T2</t>
-  </si>
-  <si>
-    <t>S27_T2</t>
-  </si>
-  <si>
-    <t>S28_T2</t>
-  </si>
-  <si>
-    <t>S29_T2</t>
-  </si>
-  <si>
-    <t>S30_T2</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>S03_T3</t>
-  </si>
-  <si>
-    <t>S04_T3</t>
-  </si>
-  <si>
-    <t>S05_T3</t>
-  </si>
-  <si>
-    <t>S06_T3</t>
-  </si>
-  <si>
-    <t>S10_T3</t>
-  </si>
-  <si>
-    <t>S12_T3</t>
-  </si>
-  <si>
-    <t>S14_T3</t>
-  </si>
-  <si>
-    <t>S16_T3</t>
-  </si>
-  <si>
-    <t>S17_T3</t>
-  </si>
-  <si>
-    <t>S21_T3</t>
-  </si>
-  <si>
-    <t>S22_T3</t>
-  </si>
-  <si>
-    <t>S24_T3</t>
-  </si>
-  <si>
-    <t>S27_T3</t>
-  </si>
-  <si>
-    <t>S28_T3</t>
-  </si>
-  <si>
-    <t>S29_T3</t>
-  </si>
-  <si>
-    <t>S30_T3</t>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>Acute</t>
   </si>
   <si>
     <t>fcsa_mixed</t>
@@ -712,9 +559,6 @@
 HR - LR p 0.43</t>
   </si>
   <si>
-    <t>Training</t>
-  </si>
-  <si>
     <t>Training_HR</t>
   </si>
   <si>
@@ -727,9 +571,6 @@
     <t>Training_LR</t>
   </si>
   <si>
-    <t>Acute</t>
-  </si>
-  <si>
     <t>Acute_HR</t>
   </si>
   <si>
@@ -739,12 +580,18 @@
     <t>HR - LR</t>
   </si>
   <si>
+    <t>T3</t>
+  </si>
+  <si>
     <t>Acute_HRvLR</t>
   </si>
   <si>
     <t>Baseline_HRvLR</t>
   </si>
   <si>
+    <t>T2</t>
+  </si>
+  <si>
     <t>Trained_HRvLR</t>
   </si>
   <si>
@@ -784,7 +631,7 @@
     <t>02_HRvLR/01_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>6fd1b8cad619c14e15d908ba9386c1cd</t>
+    <t>e706deccf806204996a968b97f852521</t>
   </si>
   <si>
     <t>variance</t>
@@ -793,7 +640,7 @@
     <t>02_HRvLR/04_Variance/c_data/variance.xlsx</t>
   </si>
   <si>
-    <t>8db87e5737d2b9edc64b992b017740a5</t>
+    <t>21f4207236305a5ac8a5be8a5cbaf4be</t>
   </si>
   <si>
     <t>slopes</t>
@@ -1539,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -1764,7 +1611,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
         <v>58</v>
@@ -1789,10 +1636,10 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1800,10 +1647,10 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1907,7 +1754,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
         <v>82</v>
@@ -1921,10 +1768,10 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" t="s">
         <v>84</v>
-      </c>
-      <c r="C35" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1932,7 +1779,7 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
         <v>86</v>
@@ -2006,13 +1853,13 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" t="s">
         <v>99</v>
-      </c>
-      <c r="C43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2020,10 +1867,10 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" t="s">
         <v>101</v>
-      </c>
-      <c r="C44" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2031,10 +1878,10 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" t="s">
         <v>103</v>
-      </c>
-      <c r="C45" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2042,10 +1889,10 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" t="s">
         <v>105</v>
-      </c>
-      <c r="C46" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -2053,10 +1900,10 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" t="s">
         <v>107</v>
-      </c>
-      <c r="C47" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -2064,10 +1911,10 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" t="s">
         <v>109</v>
-      </c>
-      <c r="C48" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -2075,10 +1922,10 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" t="s">
         <v>111</v>
-      </c>
-      <c r="C49" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -2086,10 +1933,10 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" t="s">
         <v>113</v>
-      </c>
-      <c r="C50" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -2097,10 +1944,10 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" t="s">
         <v>115</v>
-      </c>
-      <c r="C51" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -2108,10 +1955,10 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -2119,10 +1966,10 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -2130,10 +1977,10 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="C54" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -2141,10 +1988,10 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" t="s">
         <v>120</v>
-      </c>
-      <c r="C55" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -2152,10 +1999,10 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" t="s">
         <v>122</v>
-      </c>
-      <c r="C56" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -2163,10 +2010,10 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" t="s">
         <v>124</v>
-      </c>
-      <c r="C57" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -2174,10 +2021,10 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" t="s">
         <v>126</v>
-      </c>
-      <c r="C58" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -2185,21 +2032,21 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" t="s">
         <v>128</v>
-      </c>
-      <c r="C59" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B60" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" t="s">
         <v>130</v>
-      </c>
-      <c r="C60" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -2207,10 +2054,10 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" t="s">
         <v>132</v>
-      </c>
-      <c r="C61" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2218,21 +2065,21 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" t="s">
         <v>134</v>
-      </c>
-      <c r="C62" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B63" t="s">
+        <v>135</v>
+      </c>
+      <c r="C63" t="s">
         <v>136</v>
-      </c>
-      <c r="C63" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -2240,10 +2087,10 @@
         <v>16</v>
       </c>
       <c r="B64" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" t="s">
         <v>138</v>
-      </c>
-      <c r="C64" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2251,21 +2098,10 @@
         <v>16</v>
       </c>
       <c r="B65" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" t="s">
         <v>140</v>
-      </c>
-      <c r="C65" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>16</v>
-      </c>
-      <c r="B66" t="s">
-        <v>142</v>
-      </c>
-      <c r="C66" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2315,7 +2151,7 @@
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F2">
         <v>5488</v>
@@ -2331,10 +2167,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -2371,1975 +2207,1828 @@
       <c r="L1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2">
+        <v>-29.03668837129199</v>
+      </c>
+      <c r="E2">
+        <v>-36.01120412550372</v>
+      </c>
+      <c r="F2">
+        <v>0.15492</v>
+      </c>
+      <c r="G2">
+        <v>0.13464</v>
+      </c>
+      <c r="H2">
+        <v>16</v>
+      </c>
+      <c r="I2">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J2">
+        <v>0.8472</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" t="s">
         <v>145</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3">
+        <v>14.52182560559677</v>
+      </c>
+      <c r="E3">
+        <v>-11.93782150188384</v>
+      </c>
+      <c r="F3">
+        <v>0.15492</v>
+      </c>
+      <c r="G3">
+        <v>0.13464</v>
+      </c>
+      <c r="H3">
+        <v>16</v>
+      </c>
+      <c r="I3">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J3">
+        <v>0.8472</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" t="s">
         <v>146</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4">
+        <v>6.347878895134587</v>
+      </c>
+      <c r="E4">
+        <v>3.589778644910988</v>
+      </c>
+      <c r="F4">
+        <v>0.15492</v>
+      </c>
+      <c r="G4">
+        <v>0.13464</v>
+      </c>
+      <c r="H4">
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J4">
+        <v>0.8472</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" t="s">
         <v>147</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5">
+        <v>-40.40482862456631</v>
+      </c>
+      <c r="E5">
+        <v>13.76673697688079</v>
+      </c>
+      <c r="F5">
+        <v>0.15492</v>
+      </c>
+      <c r="G5">
+        <v>0.13464</v>
+      </c>
+      <c r="H5">
+        <v>16</v>
+      </c>
+      <c r="I5">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J5">
+        <v>0.8472</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" t="s">
         <v>148</v>
       </c>
-      <c r="E2">
-        <v>-29.03668837129205</v>
-      </c>
-      <c r="F2">
-        <v>-36.01120412550364</v>
-      </c>
-      <c r="G2">
+      <c r="C6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6">
+        <v>10.45489006361174</v>
+      </c>
+      <c r="E6">
+        <v>16.19130784479905</v>
+      </c>
+      <c r="F6">
         <v>0.15492</v>
       </c>
-      <c r="H2">
+      <c r="G6">
         <v>0.13464</v>
       </c>
-      <c r="I2">
+      <c r="H6">
         <v>16</v>
       </c>
-      <c r="J2">
+      <c r="I6">
         <v>0.05586338672302834</v>
       </c>
-      <c r="K2">
+      <c r="J6">
         <v>0.8472</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
         <v>-0.06666666666666667</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7">
+        <v>-1.132590706856136</v>
+      </c>
+      <c r="E7">
+        <v>29.03028571191372</v>
+      </c>
+      <c r="F7">
+        <v>0.15492</v>
+      </c>
+      <c r="G7">
+        <v>0.13464</v>
+      </c>
+      <c r="H7">
+        <v>16</v>
+      </c>
+      <c r="I7">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J7">
+        <v>0.8472</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8">
+        <v>20.46158158979756</v>
+      </c>
+      <c r="E8">
+        <v>-10.43808065911211</v>
+      </c>
+      <c r="F8">
+        <v>0.15492</v>
+      </c>
+      <c r="G8">
+        <v>0.13464</v>
+      </c>
+      <c r="H8">
+        <v>16</v>
+      </c>
+      <c r="I8">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J8">
+        <v>0.8472</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9">
+        <v>3.289723066035478</v>
+      </c>
+      <c r="E9">
+        <v>6.064156944093852</v>
+      </c>
+      <c r="F9">
+        <v>0.15492</v>
+      </c>
+      <c r="G9">
+        <v>0.13464</v>
+      </c>
+      <c r="H9">
+        <v>16</v>
+      </c>
+      <c r="I9">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J9">
+        <v>0.8472</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10">
+        <v>13.08056937520334</v>
+      </c>
+      <c r="E10">
+        <v>-2.609809670670361</v>
+      </c>
+      <c r="F10">
+        <v>0.15492</v>
+      </c>
+      <c r="G10">
+        <v>0.13464</v>
+      </c>
+      <c r="H10">
+        <v>16</v>
+      </c>
+      <c r="I10">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J10">
+        <v>0.8472</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11">
+        <v>20.60276149624735</v>
+      </c>
+      <c r="E11">
+        <v>-3.315935250493481</v>
+      </c>
+      <c r="F11">
+        <v>0.15492</v>
+      </c>
+      <c r="G11">
+        <v>0.13464</v>
+      </c>
+      <c r="H11">
+        <v>16</v>
+      </c>
+      <c r="I11">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J11">
+        <v>0.8472</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12">
+        <v>11.4309992200542</v>
+      </c>
+      <c r="E12">
+        <v>-9.030596799038737</v>
+      </c>
+      <c r="F12">
+        <v>0.15492</v>
+      </c>
+      <c r="G12">
+        <v>0.13464</v>
+      </c>
+      <c r="H12">
+        <v>16</v>
+      </c>
+      <c r="I12">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J12">
+        <v>0.8472</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13">
+        <v>7.603404674660928</v>
+      </c>
+      <c r="E13">
+        <v>-18.29477087935063</v>
+      </c>
+      <c r="F13">
+        <v>0.15492</v>
+      </c>
+      <c r="G13">
+        <v>0.13464</v>
+      </c>
+      <c r="H13">
+        <v>16</v>
+      </c>
+      <c r="I13">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J13">
+        <v>0.8472</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14">
+        <v>-1.815703959054005</v>
+      </c>
+      <c r="E14">
+        <v>26.02961413445728</v>
+      </c>
+      <c r="F14">
+        <v>0.15492</v>
+      </c>
+      <c r="G14">
+        <v>0.13464</v>
+      </c>
+      <c r="H14">
+        <v>16</v>
+      </c>
+      <c r="I14">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J14">
+        <v>0.8472</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15">
+        <v>-24.79211528765926</v>
+      </c>
+      <c r="E15">
+        <v>-7.93904705097064</v>
+      </c>
+      <c r="F15">
+        <v>0.15492</v>
+      </c>
+      <c r="G15">
+        <v>0.13464</v>
+      </c>
+      <c r="H15">
+        <v>16</v>
+      </c>
+      <c r="I15">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J15">
+        <v>0.8472</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16">
+        <v>-0.2726434558318989</v>
+      </c>
+      <c r="E16">
+        <v>-3.542544623471076</v>
+      </c>
+      <c r="F16">
+        <v>0.15492</v>
+      </c>
+      <c r="G16">
+        <v>0.13464</v>
+      </c>
+      <c r="H16">
+        <v>16</v>
+      </c>
+      <c r="I16">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J16">
+        <v>0.8472</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17">
+        <v>-10.33906358108228</v>
+      </c>
+      <c r="E17">
+        <v>8.447930303438897</v>
+      </c>
+      <c r="F17">
+        <v>0.15492</v>
+      </c>
+      <c r="G17">
+        <v>0.13464</v>
+      </c>
+      <c r="H17">
+        <v>16</v>
+      </c>
+      <c r="I17">
+        <v>0.05586338672302834</v>
+      </c>
+      <c r="J17">
+        <v>0.8472</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>-0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18">
+        <v>-21.45268611886402</v>
+      </c>
+      <c r="E18">
+        <v>24.79610899360193</v>
+      </c>
+      <c r="F18">
+        <v>0.21269</v>
+      </c>
+      <c r="G18">
+        <v>0.11632</v>
+      </c>
+      <c r="H18">
+        <v>16</v>
+      </c>
+      <c r="I18">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J18">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" t="s">
         <v>145</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19">
+        <v>30.65620820961616</v>
+      </c>
+      <c r="E19">
+        <v>7.173515860534933</v>
+      </c>
+      <c r="F19">
+        <v>0.21269</v>
+      </c>
+      <c r="G19">
+        <v>0.11632</v>
+      </c>
+      <c r="H19">
+        <v>16</v>
+      </c>
+      <c r="I19">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J19">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20">
+        <v>-13.13268726403322</v>
+      </c>
+      <c r="E20">
+        <v>-5.03134027280509</v>
+      </c>
+      <c r="F20">
+        <v>0.21269</v>
+      </c>
+      <c r="G20">
+        <v>0.11632</v>
+      </c>
+      <c r="H20">
+        <v>16</v>
+      </c>
+      <c r="I20">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J20">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21">
+        <v>-21.13657678120648</v>
+      </c>
+      <c r="E21">
+        <v>28.0805290296919</v>
+      </c>
+      <c r="F21">
+        <v>0.21269</v>
+      </c>
+      <c r="G21">
+        <v>0.11632</v>
+      </c>
+      <c r="H21">
+        <v>16</v>
+      </c>
+      <c r="I21">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J21">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22">
+        <v>14.98295857510104</v>
+      </c>
+      <c r="E22">
+        <v>-10.86846024292371</v>
+      </c>
+      <c r="F22">
+        <v>0.21269</v>
+      </c>
+      <c r="G22">
+        <v>0.11632</v>
+      </c>
+      <c r="H22">
+        <v>16</v>
+      </c>
+      <c r="I22">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J22">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>161</v>
+      </c>
+      <c r="B23" t="s">
         <v>149</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23">
+        <v>-10.77856494084534</v>
+      </c>
+      <c r="E23">
+        <v>-11.2622110953281</v>
+      </c>
+      <c r="F23">
+        <v>0.21269</v>
+      </c>
+      <c r="G23">
+        <v>0.11632</v>
+      </c>
+      <c r="H23">
+        <v>16</v>
+      </c>
+      <c r="I23">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J23">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" t="s">
         <v>150</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24">
+        <v>61.46580929732519</v>
+      </c>
+      <c r="E24">
+        <v>9.993628094622975</v>
+      </c>
+      <c r="F24">
+        <v>0.21269</v>
+      </c>
+      <c r="G24">
+        <v>0.11632</v>
+      </c>
+      <c r="H24">
+        <v>16</v>
+      </c>
+      <c r="I24">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J24">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" t="s">
         <v>151</v>
       </c>
-      <c r="E3">
-        <v>13.08056937520336</v>
-      </c>
-      <c r="F3">
-        <v>-2.609809670670416</v>
-      </c>
-      <c r="G3">
-        <v>0.15492</v>
-      </c>
-      <c r="H3">
-        <v>0.13464</v>
-      </c>
-      <c r="I3">
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25">
+        <v>-6.582695963512122</v>
+      </c>
+      <c r="E25">
+        <v>-0.0459011691414369</v>
+      </c>
+      <c r="F25">
+        <v>0.21269</v>
+      </c>
+      <c r="G25">
+        <v>0.11632</v>
+      </c>
+      <c r="H25">
         <v>16</v>
       </c>
-      <c r="J3">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K3">
-        <v>0.8472</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
+      <c r="I25">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J25">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26">
+        <v>-10.49403302399655</v>
+      </c>
+      <c r="E26">
+        <v>3.311990707811277</v>
+      </c>
+      <c r="F26">
+        <v>0.21269</v>
+      </c>
+      <c r="G26">
+        <v>0.11632</v>
+      </c>
+      <c r="H26">
+        <v>16</v>
+      </c>
+      <c r="I26">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J26">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27">
+        <v>-0.8520404240935795</v>
+      </c>
+      <c r="E27">
+        <v>-12.16807484771298</v>
+      </c>
+      <c r="F27">
+        <v>0.21269</v>
+      </c>
+      <c r="G27">
+        <v>0.11632</v>
+      </c>
+      <c r="H27">
+        <v>16</v>
+      </c>
+      <c r="I27">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J27">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28">
+        <v>-8.905161704142964</v>
+      </c>
+      <c r="E28">
+        <v>-15.59960396679755</v>
+      </c>
+      <c r="F28">
+        <v>0.21269</v>
+      </c>
+      <c r="G28">
+        <v>0.11632</v>
+      </c>
+      <c r="H28">
+        <v>16</v>
+      </c>
+      <c r="I28">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J28">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" t="s">
+        <v>153</v>
+      </c>
+      <c r="D29">
+        <v>3.673624967765215</v>
+      </c>
+      <c r="E29">
+        <v>-2.146069013034444</v>
+      </c>
+      <c r="F29">
+        <v>0.21269</v>
+      </c>
+      <c r="G29">
+        <v>0.11632</v>
+      </c>
+      <c r="H29">
+        <v>16</v>
+      </c>
+      <c r="I29">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J29">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30">
+        <v>-7.780695865248901</v>
+      </c>
+      <c r="E30">
+        <v>-34.63288692653925</v>
+      </c>
+      <c r="F30">
+        <v>0.21269</v>
+      </c>
+      <c r="G30">
+        <v>0.11632</v>
+      </c>
+      <c r="H30">
+        <v>16</v>
+      </c>
+      <c r="I30">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J30">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31">
+        <v>3.66485814620185</v>
+      </c>
+      <c r="E31">
+        <v>3.802924479326137</v>
+      </c>
+      <c r="F31">
+        <v>0.21269</v>
+      </c>
+      <c r="G31">
+        <v>0.11632</v>
+      </c>
+      <c r="H31">
+        <v>16</v>
+      </c>
+      <c r="I31">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J31">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32">
+        <v>-3.654005474511882</v>
+      </c>
+      <c r="E32">
+        <v>2.910015136522133</v>
+      </c>
+      <c r="F32">
+        <v>0.21269</v>
+      </c>
+      <c r="G32">
+        <v>0.11632</v>
+      </c>
+      <c r="H32">
+        <v>16</v>
+      </c>
+      <c r="I32">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J32">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33">
+        <v>-9.674311635554265</v>
+      </c>
+      <c r="E33">
+        <v>11.68583523217131</v>
+      </c>
+      <c r="F33">
+        <v>0.21269</v>
+      </c>
+      <c r="G33">
+        <v>0.11632</v>
+      </c>
+      <c r="H33">
+        <v>16</v>
+      </c>
+      <c r="I33">
+        <v>0.06091220503125495</v>
+      </c>
+      <c r="J33">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34">
+        <v>-14.11432723695496</v>
+      </c>
+      <c r="E34">
+        <v>-3.523808612134344</v>
+      </c>
+      <c r="F34">
+        <v>0.21137</v>
+      </c>
+      <c r="G34">
+        <v>0.14021</v>
+      </c>
+      <c r="H34">
+        <v>16</v>
+      </c>
+      <c r="I34">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J34">
+        <v>0.1655</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" t="s">
         <v>145</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C35" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35">
+        <v>-50.63670537156404</v>
+      </c>
+      <c r="E35">
+        <v>24.25884053615511</v>
+      </c>
+      <c r="F35">
+        <v>0.21137</v>
+      </c>
+      <c r="G35">
+        <v>0.14021</v>
+      </c>
+      <c r="H35">
+        <v>16</v>
+      </c>
+      <c r="I35">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J35">
+        <v>0.1655</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36">
+        <v>6.996138059323121</v>
+      </c>
+      <c r="E36">
+        <v>3.025227537870859</v>
+      </c>
+      <c r="F36">
+        <v>0.21137</v>
+      </c>
+      <c r="G36">
+        <v>0.14021</v>
+      </c>
+      <c r="H36">
+        <v>16</v>
+      </c>
+      <c r="I36">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J36">
+        <v>0.1655</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37">
+        <v>-0.6500778682620784</v>
+      </c>
+      <c r="E37">
+        <v>-2.363870545018254</v>
+      </c>
+      <c r="F37">
+        <v>0.21137</v>
+      </c>
+      <c r="G37">
+        <v>0.14021</v>
+      </c>
+      <c r="H37">
+        <v>16</v>
+      </c>
+      <c r="I37">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J37">
+        <v>0.1655</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38">
+        <v>-45.10179677976108</v>
+      </c>
+      <c r="E38">
+        <v>-30.65768310268965</v>
+      </c>
+      <c r="F38">
+        <v>0.21137</v>
+      </c>
+      <c r="G38">
+        <v>0.14021</v>
+      </c>
+      <c r="H38">
+        <v>16</v>
+      </c>
+      <c r="I38">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J38">
+        <v>0.1655</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C39" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39">
+        <v>19.10707537583495</v>
+      </c>
+      <c r="E39">
+        <v>2.592779707972325</v>
+      </c>
+      <c r="F39">
+        <v>0.21137</v>
+      </c>
+      <c r="G39">
+        <v>0.14021</v>
+      </c>
+      <c r="H39">
+        <v>16</v>
+      </c>
+      <c r="I39">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J39">
+        <v>0.1655</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40">
+        <v>1.675538076477031</v>
+      </c>
+      <c r="E40">
+        <v>-29.11045532426017</v>
+      </c>
+      <c r="F40">
+        <v>0.21137</v>
+      </c>
+      <c r="G40">
+        <v>0.14021</v>
+      </c>
+      <c r="H40">
+        <v>16</v>
+      </c>
+      <c r="I40">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J40">
+        <v>0.1655</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41">
+        <v>20.84566414077102</v>
+      </c>
+      <c r="E41">
+        <v>0.5268600809640148</v>
+      </c>
+      <c r="F41">
+        <v>0.21137</v>
+      </c>
+      <c r="G41">
+        <v>0.14021</v>
+      </c>
+      <c r="H41">
+        <v>16</v>
+      </c>
+      <c r="I41">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J41">
+        <v>0.1655</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" t="s">
         <v>152</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C42" t="s">
         <v>153</v>
       </c>
-      <c r="D4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E4">
-        <v>20.60276149624734</v>
-      </c>
-      <c r="F4">
-        <v>-3.315935250493557</v>
-      </c>
-      <c r="G4">
-        <v>0.15492</v>
-      </c>
-      <c r="H4">
-        <v>0.13464</v>
-      </c>
-      <c r="I4">
+      <c r="D42">
+        <v>11.13885990877638</v>
+      </c>
+      <c r="E42">
+        <v>-11.23486085187857</v>
+      </c>
+      <c r="F42">
+        <v>0.21137</v>
+      </c>
+      <c r="G42">
+        <v>0.14021</v>
+      </c>
+      <c r="H42">
         <v>16</v>
       </c>
-      <c r="J4">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K4">
-        <v>0.8472</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="I42">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J42">
+        <v>0.1655</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>162</v>
+      </c>
+      <c r="B43" t="s">
         <v>154</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C43" t="s">
+        <v>153</v>
+      </c>
+      <c r="D43">
+        <v>18.81592132947557</v>
+      </c>
+      <c r="E43">
+        <v>-4.200272839149616</v>
+      </c>
+      <c r="F43">
+        <v>0.21137</v>
+      </c>
+      <c r="G43">
+        <v>0.14021</v>
+      </c>
+      <c r="H43">
+        <v>16</v>
+      </c>
+      <c r="I43">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J43">
+        <v>0.1655</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" t="s">
+        <v>162</v>
+      </c>
+      <c r="B44" t="s">
         <v>155</v>
       </c>
-      <c r="D5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5">
-        <v>11.43099922005418</v>
-      </c>
-      <c r="F5">
-        <v>-9.030596799038776</v>
-      </c>
-      <c r="G5">
-        <v>0.15492</v>
-      </c>
-      <c r="H5">
-        <v>0.13464</v>
-      </c>
-      <c r="I5">
+      <c r="C44" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44">
+        <v>5.333622346347253</v>
+      </c>
+      <c r="E44">
+        <v>4.269631418755687</v>
+      </c>
+      <c r="F44">
+        <v>0.21137</v>
+      </c>
+      <c r="G44">
+        <v>0.14021</v>
+      </c>
+      <c r="H44">
         <v>16</v>
       </c>
-      <c r="J5">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K5">
-        <v>0.8472</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="I44">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J44">
+        <v>0.1655</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" t="s">
         <v>156</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C45" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45">
+        <v>8.916715707470596</v>
+      </c>
+      <c r="E45">
+        <v>5.866320463704772</v>
+      </c>
+      <c r="F45">
+        <v>0.21137</v>
+      </c>
+      <c r="G45">
+        <v>0.14021</v>
+      </c>
+      <c r="H45">
+        <v>16</v>
+      </c>
+      <c r="I45">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J45">
+        <v>0.1655</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" t="s">
         <v>157</v>
       </c>
-      <c r="D6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6">
-        <v>14.52182560559675</v>
-      </c>
-      <c r="F6">
-        <v>-11.9378215018839</v>
-      </c>
-      <c r="G6">
-        <v>0.15492</v>
-      </c>
-      <c r="H6">
-        <v>0.13464</v>
-      </c>
-      <c r="I6">
+      <c r="C46" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46">
+        <v>5.027703058812455</v>
+      </c>
+      <c r="E46">
+        <v>32.08900539203711</v>
+      </c>
+      <c r="F46">
+        <v>0.21137</v>
+      </c>
+      <c r="G46">
+        <v>0.14021</v>
+      </c>
+      <c r="H46">
         <v>16</v>
       </c>
-      <c r="J6">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K6">
-        <v>0.8472</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="I46">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J46">
+        <v>0.1655</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" t="s">
+        <v>162</v>
+      </c>
+      <c r="B47" t="s">
         <v>158</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C47" t="s">
+        <v>153</v>
+      </c>
+      <c r="D47">
+        <v>-6.877154736840926</v>
+      </c>
+      <c r="E47">
+        <v>23.31630246770189</v>
+      </c>
+      <c r="F47">
+        <v>0.21137</v>
+      </c>
+      <c r="G47">
+        <v>0.14021</v>
+      </c>
+      <c r="H47">
+        <v>16</v>
+      </c>
+      <c r="I47">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J47">
+        <v>0.1655</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>162</v>
+      </c>
+      <c r="B48" t="s">
         <v>159</v>
       </c>
-      <c r="D7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7">
-        <v>7.603404674660883</v>
-      </c>
-      <c r="F7">
-        <v>-18.29477087935067</v>
-      </c>
-      <c r="G7">
-        <v>0.15492</v>
-      </c>
-      <c r="H7">
-        <v>0.13464</v>
-      </c>
-      <c r="I7">
+      <c r="C48" t="s">
+        <v>153</v>
+      </c>
+      <c r="D48">
+        <v>13.61621960807793</v>
+      </c>
+      <c r="E48">
+        <v>-2.940079328019769</v>
+      </c>
+      <c r="F48">
+        <v>0.21137</v>
+      </c>
+      <c r="G48">
+        <v>0.14021</v>
+      </c>
+      <c r="H48">
         <v>16</v>
       </c>
-      <c r="J7">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K7">
-        <v>0.8472</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="I48">
+        <v>0.0795016460946099</v>
+      </c>
+      <c r="J48">
+        <v>0.1655</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" t="s">
         <v>160</v>
       </c>
-      <c r="C8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8">
-        <v>-1.815703959053951</v>
-      </c>
-      <c r="F8">
-        <v>26.0296141344573</v>
-      </c>
-      <c r="G8">
-        <v>0.15492</v>
-      </c>
-      <c r="H8">
-        <v>0.13464</v>
-      </c>
-      <c r="I8">
+      <c r="C49" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49">
+        <v>5.906604382016643</v>
+      </c>
+      <c r="E49">
+        <v>-11.9139370020114</v>
+      </c>
+      <c r="F49">
+        <v>0.21137</v>
+      </c>
+      <c r="G49">
+        <v>0.14021</v>
+      </c>
+      <c r="H49">
         <v>16</v>
       </c>
-      <c r="J8">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K8">
-        <v>0.8472</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>145</v>
-      </c>
-      <c r="B9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9">
-        <v>6.347878895134601</v>
-      </c>
-      <c r="F9">
-        <v>3.589778644910965</v>
-      </c>
-      <c r="G9">
-        <v>0.15492</v>
-      </c>
-      <c r="H9">
-        <v>0.13464</v>
-      </c>
-      <c r="I9">
-        <v>16</v>
-      </c>
-      <c r="J9">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K9">
-        <v>0.8472</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" t="s">
-        <v>164</v>
-      </c>
-      <c r="C10" t="s">
-        <v>165</v>
-      </c>
-      <c r="D10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10">
-        <v>-24.7921152876593</v>
-      </c>
-      <c r="F10">
-        <v>-7.939047050970563</v>
-      </c>
-      <c r="G10">
-        <v>0.15492</v>
-      </c>
-      <c r="H10">
-        <v>0.13464</v>
-      </c>
-      <c r="I10">
-        <v>16</v>
-      </c>
-      <c r="J10">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K10">
-        <v>0.8472</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B11" t="s">
-        <v>166</v>
-      </c>
-      <c r="C11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11">
-        <v>-0.2726434558319107</v>
-      </c>
-      <c r="F11">
-        <v>-3.542544623471068</v>
-      </c>
-      <c r="G11">
-        <v>0.15492</v>
-      </c>
-      <c r="H11">
-        <v>0.13464</v>
-      </c>
-      <c r="I11">
-        <v>16</v>
-      </c>
-      <c r="J11">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K11">
-        <v>0.8472</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>145</v>
-      </c>
-      <c r="B12" t="s">
-        <v>168</v>
-      </c>
-      <c r="C12" t="s">
-        <v>169</v>
-      </c>
-      <c r="D12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E12">
-        <v>-40.40482862456627</v>
-      </c>
-      <c r="F12">
-        <v>13.76673697688087</v>
-      </c>
-      <c r="G12">
-        <v>0.15492</v>
-      </c>
-      <c r="H12">
-        <v>0.13464</v>
-      </c>
-      <c r="I12">
-        <v>16</v>
-      </c>
-      <c r="J12">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K12">
-        <v>0.8472</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>145</v>
-      </c>
-      <c r="B13" t="s">
-        <v>170</v>
-      </c>
-      <c r="C13" t="s">
-        <v>171</v>
-      </c>
-      <c r="D13" t="s">
-        <v>148</v>
-      </c>
-      <c r="E13">
-        <v>10.45489006361177</v>
-      </c>
-      <c r="F13">
-        <v>16.19130784479903</v>
-      </c>
-      <c r="G13">
-        <v>0.15492</v>
-      </c>
-      <c r="H13">
-        <v>0.13464</v>
-      </c>
-      <c r="I13">
-        <v>16</v>
-      </c>
-      <c r="J13">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K13">
-        <v>0.8472</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D14" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14">
-        <v>-1.132590706856068</v>
-      </c>
-      <c r="F14">
-        <v>29.03028571191373</v>
-      </c>
-      <c r="G14">
-        <v>0.15492</v>
-      </c>
-      <c r="H14">
-        <v>0.13464</v>
-      </c>
-      <c r="I14">
-        <v>16</v>
-      </c>
-      <c r="J14">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K14">
-        <v>0.8472</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B15" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15" t="s">
-        <v>175</v>
-      </c>
-      <c r="D15" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15">
-        <v>20.46158158979754</v>
-      </c>
-      <c r="F15">
-        <v>-10.43808065911218</v>
-      </c>
-      <c r="G15">
-        <v>0.15492</v>
-      </c>
-      <c r="H15">
-        <v>0.13464</v>
-      </c>
-      <c r="I15">
-        <v>16</v>
-      </c>
-      <c r="J15">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K15">
-        <v>0.8472</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>145</v>
-      </c>
-      <c r="B16" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" t="s">
-        <v>177</v>
-      </c>
-      <c r="D16" t="s">
-        <v>148</v>
-      </c>
-      <c r="E16">
-        <v>3.289723066035493</v>
-      </c>
-      <c r="F16">
-        <v>6.064156944093871</v>
-      </c>
-      <c r="G16">
-        <v>0.15492</v>
-      </c>
-      <c r="H16">
-        <v>0.13464</v>
-      </c>
-      <c r="I16">
-        <v>16</v>
-      </c>
-      <c r="J16">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K16">
-        <v>0.8472</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>145</v>
-      </c>
-      <c r="B17" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" t="s">
-        <v>179</v>
-      </c>
-      <c r="D17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E17">
-        <v>-10.33906358108227</v>
-      </c>
-      <c r="F17">
-        <v>8.44793030343892</v>
-      </c>
-      <c r="G17">
-        <v>0.15492</v>
-      </c>
-      <c r="H17">
-        <v>0.13464</v>
-      </c>
-      <c r="I17">
-        <v>16</v>
-      </c>
-      <c r="J17">
-        <v>0.05586338672302834</v>
-      </c>
-      <c r="K17">
-        <v>0.8472</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>-0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>180</v>
-      </c>
-      <c r="B18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C18" t="s">
-        <v>147</v>
-      </c>
-      <c r="D18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18">
-        <v>-3.199725992983305</v>
-      </c>
-      <c r="F18">
-        <v>2.269819759171599</v>
-      </c>
-      <c r="G18">
-        <v>0.23726</v>
-      </c>
-      <c r="H18">
-        <v>0.12445</v>
-      </c>
-      <c r="I18">
-        <v>16</v>
-      </c>
-      <c r="J18">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K18">
-        <v>0.2796</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" t="s">
-        <v>180</v>
-      </c>
-      <c r="B19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19">
-        <v>-18.30102171593667</v>
-      </c>
-      <c r="F19">
-        <v>27.47948371907972</v>
-      </c>
-      <c r="G19">
-        <v>0.23726</v>
-      </c>
-      <c r="H19">
-        <v>0.12445</v>
-      </c>
-      <c r="I19">
-        <v>16</v>
-      </c>
-      <c r="J19">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K19">
-        <v>0.2796</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
-        <v>180</v>
-      </c>
-      <c r="B20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C20" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20">
-        <v>-12.35518630816837</v>
-      </c>
-      <c r="F20">
-        <v>20.47853459320237</v>
-      </c>
-      <c r="G20">
-        <v>0.23726</v>
-      </c>
-      <c r="H20">
-        <v>0.12445</v>
-      </c>
-      <c r="I20">
-        <v>16</v>
-      </c>
-      <c r="J20">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K20">
-        <v>0.2796</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
-        <v>180</v>
-      </c>
-      <c r="B21" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D21" t="s">
-        <v>151</v>
-      </c>
-      <c r="E21">
-        <v>-5.98885249352225</v>
-      </c>
-      <c r="F21">
-        <v>0.05369352558512538</v>
-      </c>
-      <c r="G21">
-        <v>0.23726</v>
-      </c>
-      <c r="H21">
-        <v>0.12445</v>
-      </c>
-      <c r="I21">
-        <v>16</v>
-      </c>
-      <c r="J21">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K21">
-        <v>0.2796</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" t="s">
-        <v>180</v>
-      </c>
-      <c r="B22" t="s">
-        <v>185</v>
-      </c>
-      <c r="C22" t="s">
-        <v>157</v>
-      </c>
-      <c r="D22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22">
-        <v>31.62719350495113</v>
-      </c>
-      <c r="F22">
-        <v>-12.12352850493933</v>
-      </c>
-      <c r="G22">
-        <v>0.23726</v>
-      </c>
-      <c r="H22">
-        <v>0.12445</v>
-      </c>
-      <c r="I22">
-        <v>16</v>
-      </c>
-      <c r="J22">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K22">
-        <v>0.2796</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" t="s">
-        <v>180</v>
-      </c>
-      <c r="B23" t="s">
-        <v>186</v>
-      </c>
-      <c r="C23" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" t="s">
-        <v>151</v>
-      </c>
-      <c r="E23">
-        <v>3.109524346521162</v>
-      </c>
-      <c r="F23">
-        <v>8.541822036012034</v>
-      </c>
-      <c r="G23">
-        <v>0.23726</v>
-      </c>
-      <c r="H23">
-        <v>0.12445</v>
-      </c>
-      <c r="I23">
-        <v>16</v>
-      </c>
-      <c r="J23">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K23">
-        <v>0.2796</v>
-      </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" t="s">
-        <v>180</v>
-      </c>
-      <c r="B24" t="s">
-        <v>187</v>
-      </c>
-      <c r="C24" t="s">
-        <v>161</v>
-      </c>
-      <c r="D24" t="s">
-        <v>151</v>
-      </c>
-      <c r="E24">
-        <v>-18.5075133674658</v>
-      </c>
-      <c r="F24">
-        <v>-42.00602050420362</v>
-      </c>
-      <c r="G24">
-        <v>0.23726</v>
-      </c>
-      <c r="H24">
-        <v>0.12445</v>
-      </c>
-      <c r="I24">
-        <v>16</v>
-      </c>
-      <c r="J24">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K24">
-        <v>0.2796</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" t="s">
-        <v>180</v>
-      </c>
-      <c r="B25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C25" t="s">
-        <v>163</v>
-      </c>
-      <c r="D25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E25">
-        <v>-8.841103606115809</v>
-      </c>
-      <c r="F25">
-        <v>0.07895788337331337</v>
-      </c>
-      <c r="G25">
-        <v>0.23726</v>
-      </c>
-      <c r="H25">
-        <v>0.12445</v>
-      </c>
-      <c r="I25">
-        <v>16</v>
-      </c>
-      <c r="J25">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K25">
-        <v>0.2796</v>
-      </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" t="s">
-        <v>180</v>
-      </c>
-      <c r="B26" t="s">
-        <v>189</v>
-      </c>
-      <c r="C26" t="s">
-        <v>165</v>
-      </c>
-      <c r="D26" t="s">
-        <v>151</v>
-      </c>
-      <c r="E26">
-        <v>19.44216629968949</v>
-      </c>
-      <c r="F26">
-        <v>19.25503704136196</v>
-      </c>
-      <c r="G26">
-        <v>0.23726</v>
-      </c>
-      <c r="H26">
-        <v>0.12445</v>
-      </c>
-      <c r="I26">
-        <v>16</v>
-      </c>
-      <c r="J26">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K26">
-        <v>0.2796</v>
-      </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" t="s">
-        <v>180</v>
-      </c>
-      <c r="B27" t="s">
-        <v>190</v>
-      </c>
-      <c r="C27" t="s">
-        <v>167</v>
-      </c>
-      <c r="D27" t="s">
-        <v>151</v>
-      </c>
-      <c r="E27">
-        <v>-3.221146978052823</v>
-      </c>
-      <c r="F27">
-        <v>-7.036446330564504</v>
-      </c>
-      <c r="G27">
-        <v>0.23726</v>
-      </c>
-      <c r="H27">
-        <v>0.12445</v>
-      </c>
-      <c r="I27">
-        <v>16</v>
-      </c>
-      <c r="J27">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K27">
-        <v>0.2796</v>
-      </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" t="s">
-        <v>180</v>
-      </c>
-      <c r="B28" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" t="s">
-        <v>169</v>
-      </c>
-      <c r="D28" t="s">
-        <v>148</v>
-      </c>
-      <c r="E28">
-        <v>-14.42742049074879</v>
-      </c>
-      <c r="F28">
-        <v>-5.303314698967057</v>
-      </c>
-      <c r="G28">
-        <v>0.23726</v>
-      </c>
-      <c r="H28">
-        <v>0.12445</v>
-      </c>
-      <c r="I28">
-        <v>16</v>
-      </c>
-      <c r="J28">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K28">
-        <v>0.2796</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" t="s">
-        <v>180</v>
-      </c>
-      <c r="B29" t="s">
-        <v>192</v>
-      </c>
-      <c r="C29" t="s">
-        <v>171</v>
-      </c>
-      <c r="D29" t="s">
-        <v>148</v>
-      </c>
-      <c r="E29">
-        <v>8.887449114901896</v>
-      </c>
-      <c r="F29">
-        <v>8.047642762147845</v>
-      </c>
-      <c r="G29">
-        <v>0.23726</v>
-      </c>
-      <c r="H29">
-        <v>0.12445</v>
-      </c>
-      <c r="I29">
-        <v>16</v>
-      </c>
-      <c r="J29">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K29">
-        <v>0.2796</v>
-      </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" t="s">
-        <v>180</v>
-      </c>
-      <c r="B30" t="s">
-        <v>193</v>
-      </c>
-      <c r="C30" t="s">
-        <v>173</v>
-      </c>
-      <c r="D30" t="s">
-        <v>148</v>
-      </c>
-      <c r="E30">
-        <v>-16.79140477818959</v>
-      </c>
-      <c r="F30">
-        <v>-6.980234380527873</v>
-      </c>
-      <c r="G30">
-        <v>0.23726</v>
-      </c>
-      <c r="H30">
-        <v>0.12445</v>
-      </c>
-      <c r="I30">
-        <v>16</v>
-      </c>
-      <c r="J30">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K30">
-        <v>0.2796</v>
-      </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" t="s">
-        <v>180</v>
-      </c>
-      <c r="B31" t="s">
-        <v>194</v>
-      </c>
-      <c r="C31" t="s">
-        <v>175</v>
-      </c>
-      <c r="D31" t="s">
-        <v>148</v>
-      </c>
-      <c r="E31">
-        <v>63.75873513528938</v>
-      </c>
-      <c r="F31">
-        <v>-5.894561581959279</v>
-      </c>
-      <c r="G31">
-        <v>0.23726</v>
-      </c>
-      <c r="H31">
-        <v>0.12445</v>
-      </c>
-      <c r="I31">
-        <v>16</v>
-      </c>
-      <c r="J31">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K31">
-        <v>0.2796</v>
-      </c>
-      <c r="L31">
-        <v>1</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" t="s">
-        <v>180</v>
-      </c>
-      <c r="B32" t="s">
-        <v>195</v>
-      </c>
-      <c r="C32" t="s">
-        <v>177</v>
-      </c>
-      <c r="D32" t="s">
-        <v>148</v>
-      </c>
-      <c r="E32">
-        <v>-9.817522832852235</v>
-      </c>
-      <c r="F32">
-        <v>-8.687509490290129</v>
-      </c>
-      <c r="G32">
-        <v>0.23726</v>
-      </c>
-      <c r="H32">
-        <v>0.12445</v>
-      </c>
-      <c r="I32">
-        <v>16</v>
-      </c>
-      <c r="J32">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K32">
-        <v>0.2796</v>
-      </c>
-      <c r="L32">
-        <v>1</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" t="s">
-        <v>180</v>
-      </c>
-      <c r="B33" t="s">
-        <v>196</v>
-      </c>
-      <c r="C33" t="s">
-        <v>179</v>
-      </c>
-      <c r="D33" t="s">
-        <v>151</v>
-      </c>
-      <c r="E33">
-        <v>-15.37416983731738</v>
-      </c>
-      <c r="F33">
-        <v>1.8266241715178</v>
-      </c>
-      <c r="G33">
-        <v>0.23726</v>
-      </c>
-      <c r="H33">
-        <v>0.12445</v>
-      </c>
-      <c r="I33">
-        <v>16</v>
-      </c>
-      <c r="J33">
-        <v>0.07283316473583225</v>
-      </c>
-      <c r="K33">
-        <v>0.2796</v>
-      </c>
-      <c r="L33">
-        <v>1</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" t="s">
-        <v>197</v>
-      </c>
-      <c r="B34" t="s">
-        <v>198</v>
-      </c>
-      <c r="C34" t="s">
-        <v>147</v>
-      </c>
-      <c r="D34" t="s">
-        <v>148</v>
-      </c>
-      <c r="E34">
-        <v>-13.71325990712873</v>
-      </c>
-      <c r="F34">
-        <v>1.776556329338708</v>
-      </c>
-      <c r="G34">
-        <v>0.26032</v>
-      </c>
-      <c r="H34">
-        <v>0.17011</v>
-      </c>
-      <c r="I34">
-        <v>16</v>
-      </c>
-      <c r="J34">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K34">
-        <v>0.2933</v>
-      </c>
-      <c r="L34">
-        <v>1</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" t="s">
-        <v>197</v>
-      </c>
-      <c r="B35" t="s">
-        <v>199</v>
-      </c>
-      <c r="C35" t="s">
-        <v>150</v>
-      </c>
-      <c r="D35" t="s">
-        <v>151</v>
-      </c>
-      <c r="E35">
-        <v>-4.835157290732149</v>
-      </c>
-      <c r="F35">
-        <v>-11.70520844580549</v>
-      </c>
-      <c r="G35">
-        <v>0.26032</v>
-      </c>
-      <c r="H35">
-        <v>0.17011</v>
-      </c>
-      <c r="I35">
-        <v>16</v>
-      </c>
-      <c r="J35">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K35">
-        <v>0.2933</v>
-      </c>
-      <c r="L35">
-        <v>1</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" t="s">
-        <v>197</v>
-      </c>
-      <c r="B36" t="s">
-        <v>200</v>
-      </c>
-      <c r="C36" t="s">
-        <v>153</v>
-      </c>
-      <c r="D36" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36">
-        <v>8.539242593660607</v>
-      </c>
-      <c r="F36">
-        <v>-14.88569414459188</v>
-      </c>
-      <c r="G36">
-        <v>0.26032</v>
-      </c>
-      <c r="H36">
-        <v>0.17011</v>
-      </c>
-      <c r="I36">
-        <v>16</v>
-      </c>
-      <c r="J36">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K36">
-        <v>0.2933</v>
-      </c>
-      <c r="L36">
-        <v>1</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" t="s">
-        <v>197</v>
-      </c>
-      <c r="B37" t="s">
-        <v>201</v>
-      </c>
-      <c r="C37" t="s">
-        <v>155</v>
-      </c>
-      <c r="D37" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37">
-        <v>-1.249855280976475</v>
-      </c>
-      <c r="F37">
-        <v>-12.32062532898931</v>
-      </c>
-      <c r="G37">
-        <v>0.26032</v>
-      </c>
-      <c r="H37">
-        <v>0.17011</v>
-      </c>
-      <c r="I37">
-        <v>16</v>
-      </c>
-      <c r="J37">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K37">
-        <v>0.2933</v>
-      </c>
-      <c r="L37">
-        <v>1</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" t="s">
-        <v>197</v>
-      </c>
-      <c r="B38" t="s">
-        <v>202</v>
-      </c>
-      <c r="C38" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" t="s">
-        <v>148</v>
-      </c>
-      <c r="E38">
-        <v>-23.4297593894653</v>
-      </c>
-      <c r="F38">
-        <v>21.82609225993943</v>
-      </c>
-      <c r="G38">
-        <v>0.26032</v>
-      </c>
-      <c r="H38">
-        <v>0.17011</v>
-      </c>
-      <c r="I38">
-        <v>16</v>
-      </c>
-      <c r="J38">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K38">
-        <v>0.2933</v>
-      </c>
-      <c r="L38">
-        <v>1</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" t="s">
-        <v>197</v>
-      </c>
-      <c r="B39" t="s">
-        <v>203</v>
-      </c>
-      <c r="C39" t="s">
-        <v>159</v>
-      </c>
-      <c r="D39" t="s">
-        <v>151</v>
-      </c>
-      <c r="E39">
-        <v>6.999856436791639</v>
-      </c>
-      <c r="F39">
-        <v>-17.06809356030474</v>
-      </c>
-      <c r="G39">
-        <v>0.26032</v>
-      </c>
-      <c r="H39">
-        <v>0.17011</v>
-      </c>
-      <c r="I39">
-        <v>16</v>
-      </c>
-      <c r="J39">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K39">
-        <v>0.2933</v>
-      </c>
-      <c r="L39">
-        <v>1</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="A40" t="s">
-        <v>197</v>
-      </c>
-      <c r="B40" t="s">
-        <v>204</v>
-      </c>
-      <c r="C40" t="s">
-        <v>161</v>
-      </c>
-      <c r="D40" t="s">
-        <v>151</v>
-      </c>
-      <c r="E40">
-        <v>-23.08582380590919</v>
-      </c>
-      <c r="F40">
-        <v>0.9228814963046097</v>
-      </c>
-      <c r="G40">
-        <v>0.26032</v>
-      </c>
-      <c r="H40">
-        <v>0.17011</v>
-      </c>
-      <c r="I40">
-        <v>16</v>
-      </c>
-      <c r="J40">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K40">
-        <v>0.2933</v>
-      </c>
-      <c r="L40">
-        <v>1</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" t="s">
-        <v>197</v>
-      </c>
-      <c r="B41" t="s">
-        <v>205</v>
-      </c>
-      <c r="C41" t="s">
-        <v>163</v>
-      </c>
-      <c r="D41" t="s">
-        <v>148</v>
-      </c>
-      <c r="E41">
-        <v>-2.196901127944684</v>
-      </c>
-      <c r="F41">
-        <v>-11.49009863459426</v>
-      </c>
-      <c r="G41">
-        <v>0.26032</v>
-      </c>
-      <c r="H41">
-        <v>0.17011</v>
-      </c>
-      <c r="I41">
-        <v>16</v>
-      </c>
-      <c r="J41">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K41">
-        <v>0.2933</v>
-      </c>
-      <c r="L41">
-        <v>1</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" t="s">
-        <v>197</v>
-      </c>
-      <c r="B42" t="s">
-        <v>206</v>
-      </c>
-      <c r="C42" t="s">
-        <v>165</v>
-      </c>
-      <c r="D42" t="s">
-        <v>151</v>
-      </c>
-      <c r="E42">
-        <v>-3.759322107605664</v>
-      </c>
-      <c r="F42">
-        <v>-7.38138146184473</v>
-      </c>
-      <c r="G42">
-        <v>0.26032</v>
-      </c>
-      <c r="H42">
-        <v>0.17011</v>
-      </c>
-      <c r="I42">
-        <v>16</v>
-      </c>
-      <c r="J42">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K42">
-        <v>0.2933</v>
-      </c>
-      <c r="L42">
-        <v>1</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
-      <c r="A43" t="s">
-        <v>197</v>
-      </c>
-      <c r="B43" t="s">
-        <v>207</v>
-      </c>
-      <c r="C43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D43" t="s">
-        <v>151</v>
-      </c>
-      <c r="E43">
-        <v>11.4734514780776</v>
-      </c>
-      <c r="F43">
-        <v>-6.458964603767043</v>
-      </c>
-      <c r="G43">
-        <v>0.26032</v>
-      </c>
-      <c r="H43">
-        <v>0.17011</v>
-      </c>
-      <c r="I43">
-        <v>16</v>
-      </c>
-      <c r="J43">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K43">
-        <v>0.2933</v>
-      </c>
-      <c r="L43">
-        <v>1</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="A44" t="s">
-        <v>197</v>
-      </c>
-      <c r="B44" t="s">
-        <v>208</v>
-      </c>
-      <c r="C44" t="s">
-        <v>169</v>
-      </c>
-      <c r="D44" t="s">
-        <v>148</v>
-      </c>
-      <c r="E44">
-        <v>-12.95525034438228</v>
-      </c>
-      <c r="F44">
-        <v>6.75792926484867</v>
-      </c>
-      <c r="G44">
-        <v>0.26032</v>
-      </c>
-      <c r="H44">
-        <v>0.17011</v>
-      </c>
-      <c r="I44">
-        <v>16</v>
-      </c>
-      <c r="J44">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K44">
-        <v>0.2933</v>
-      </c>
-      <c r="L44">
-        <v>1</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" t="s">
-        <v>197</v>
-      </c>
-      <c r="B45" t="s">
-        <v>209</v>
-      </c>
-      <c r="C45" t="s">
-        <v>171</v>
-      </c>
-      <c r="D45" t="s">
-        <v>148</v>
-      </c>
-      <c r="E45">
-        <v>-23.52364066028841</v>
-      </c>
-      <c r="F45">
-        <v>50.28489661480204</v>
-      </c>
-      <c r="G45">
-        <v>0.26032</v>
-      </c>
-      <c r="H45">
-        <v>0.17011</v>
-      </c>
-      <c r="I45">
-        <v>16</v>
-      </c>
-      <c r="J45">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K45">
-        <v>0.2933</v>
-      </c>
-      <c r="L45">
-        <v>1</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" t="s">
-        <v>197</v>
-      </c>
-      <c r="B46" t="s">
-        <v>210</v>
-      </c>
-      <c r="C46" t="s">
-        <v>173</v>
-      </c>
-      <c r="D46" t="s">
-        <v>148</v>
-      </c>
-      <c r="E46">
-        <v>5.06439977679006</v>
-      </c>
-      <c r="F46">
-        <v>-11.91461890555483</v>
-      </c>
-      <c r="G46">
-        <v>0.26032</v>
-      </c>
-      <c r="H46">
-        <v>0.17011</v>
-      </c>
-      <c r="I46">
-        <v>16</v>
-      </c>
-      <c r="J46">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K46">
-        <v>0.2933</v>
-      </c>
-      <c r="L46">
-        <v>1</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" t="s">
-        <v>197</v>
-      </c>
-      <c r="B47" t="s">
-        <v>211</v>
-      </c>
-      <c r="C47" t="s">
-        <v>175</v>
-      </c>
-      <c r="D47" t="s">
-        <v>148</v>
-      </c>
-      <c r="E47">
-        <v>74.73772560814433</v>
-      </c>
-      <c r="F47">
-        <v>28.90515466293769</v>
-      </c>
-      <c r="G47">
-        <v>0.26032</v>
-      </c>
-      <c r="H47">
-        <v>0.17011</v>
-      </c>
-      <c r="I47">
-        <v>16</v>
-      </c>
-      <c r="J47">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K47">
-        <v>0.2933</v>
-      </c>
-      <c r="L47">
-        <v>1</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" t="s">
-        <v>197</v>
-      </c>
-      <c r="B48" t="s">
-        <v>212</v>
-      </c>
-      <c r="C48" t="s">
-        <v>177</v>
-      </c>
-      <c r="D48" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48">
-        <v>8.668031025307945</v>
-      </c>
-      <c r="F48">
-        <v>-12.52619019586733</v>
-      </c>
-      <c r="G48">
-        <v>0.26032</v>
-      </c>
-      <c r="H48">
-        <v>0.17011</v>
-      </c>
-      <c r="I48">
-        <v>16</v>
-      </c>
-      <c r="J48">
-        <v>0.0715354531530991</v>
-      </c>
-      <c r="K48">
-        <v>0.2933</v>
-      </c>
-      <c r="L48">
-        <v>1</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="A49" t="s">
-        <v>197</v>
-      </c>
-      <c r="B49" t="s">
-        <v>213</v>
-      </c>
-      <c r="C49" t="s">
-        <v>179</v>
-      </c>
-      <c r="D49" t="s">
-        <v>151</v>
-      </c>
-      <c r="E49">
-        <v>-6.733737004339182</v>
-      </c>
-      <c r="F49">
-        <v>-4.72263534685163</v>
-      </c>
-      <c r="G49">
-        <v>0.26032</v>
-      </c>
-      <c r="H49">
-        <v>0.17011</v>
-      </c>
       <c r="I49">
-        <v>16</v>
+        <v>0.0795016460946099</v>
       </c>
       <c r="J49">
-        <v>0.0715354531530991</v>
+        <v>0.1655</v>
       </c>
       <c r="K49">
-        <v>0.2933</v>
+        <v>1</v>
       </c>
       <c r="L49">
-        <v>1</v>
-      </c>
-      <c r="M49">
         <v>0</v>
       </c>
     </row>
@@ -4355,54 +4044,54 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -4426,10 +4115,10 @@
         <v>0.001713171134239212</v>
       </c>
       <c r="K2" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="L2" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -4437,13 +4126,13 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D3">
         <v>8</v>
@@ -4467,10 +4156,10 @@
         <v>0.001713171134239212</v>
       </c>
       <c r="K3" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="L3" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -4478,13 +4167,13 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -4508,10 +4197,10 @@
         <v>0.01023059163043604</v>
       </c>
       <c r="K4" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="L4" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
@@ -4519,13 +4208,13 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -4549,10 +4238,10 @@
         <v>0.01023059163043604</v>
       </c>
       <c r="K5" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="L5" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -4560,13 +4249,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="B6" t="b">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -4590,10 +4279,10 @@
         <v>0.002763676599144667</v>
       </c>
       <c r="K6" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="L6" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -4601,13 +4290,13 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="B7" t="b">
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -4631,10 +4320,10 @@
         <v>0.002763676599144667</v>
       </c>
       <c r="K7" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="L7" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -4642,13 +4331,13 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="B8" t="b">
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D8">
         <v>8</v>
@@ -4672,10 +4361,10 @@
         <v>0.00100838258081328</v>
       </c>
       <c r="K8" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="L8" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -4683,13 +4372,13 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="B9" t="b">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -4713,10 +4402,10 @@
         <v>0.00100838258081328</v>
       </c>
       <c r="K9" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="L9" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -4724,13 +4413,13 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="B10" t="b">
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -4754,10 +4443,10 @@
         <v>0.8464533285112503</v>
       </c>
       <c r="K10" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="L10" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="M10" t="b">
         <v>1</v>
@@ -4765,13 +4454,13 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="B11" t="b">
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -4795,10 +4484,10 @@
         <v>0.8464533285112503</v>
       </c>
       <c r="K11" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="L11" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="M11" t="b">
         <v>1</v>
@@ -4806,13 +4495,13 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B12" t="b">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -4836,10 +4525,10 @@
         <v>0.4262518511068021</v>
       </c>
       <c r="K12" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="L12" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="M12" t="b">
         <v>1</v>
@@ -4847,13 +4536,13 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B13" t="b">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -4877,10 +4566,10 @@
         <v>0.4262518511068021</v>
       </c>
       <c r="K13" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
@@ -4898,45 +4587,45 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="D2" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E2">
         <v>2059</v>
@@ -4956,16 +4645,16 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="E3">
         <v>2059</v>
@@ -4985,16 +4674,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="D4" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E4">
         <v>2059</v>
@@ -5014,16 +4703,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="D5" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="E5">
         <v>2059</v>
@@ -5043,16 +4732,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="D6" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E6">
         <v>2059</v>
@@ -5072,16 +4761,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="E7">
         <v>2059</v>
@@ -5101,16 +4790,16 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C8" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="D8" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E8">
         <v>2059</v>
@@ -5130,16 +4819,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="E9">
         <v>2059</v>
@@ -5159,16 +4848,16 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>236</v>
+        <v>183</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="D10" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E10">
         <v>2059</v>
@@ -5188,16 +4877,16 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>236</v>
+        <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C11" t="s">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="E11">
         <v>2059</v>
@@ -5217,16 +4906,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>236</v>
+        <v>183</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C12" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="D12" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E12">
         <v>2059</v>
@@ -5246,16 +4935,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>236</v>
+        <v>183</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C13" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="D13" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="E13">
         <v>2059</v>
@@ -5275,16 +4964,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>236</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C14" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="D14" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E14">
         <v>2059</v>
@@ -5304,16 +4993,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>236</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C15" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="D15" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="E15">
         <v>2059</v>
@@ -5333,16 +5022,16 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="C16" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="D16" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E16">
         <v>2059</v>
@@ -5362,16 +5051,16 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="C17" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="D17" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="E17">
         <v>2059</v>
@@ -5391,16 +5080,16 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="C18" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="D18" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E18">
         <v>2059</v>
@@ -5420,16 +5109,16 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="C19" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="E19">
         <v>2059</v>
@@ -5459,72 +5148,72 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="E2" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="F2">
         <v>49</v>
@@ -5533,13 +5222,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="I2" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="J2" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="K2">
         <v>0.02811640096906698</v>
@@ -5548,7 +5237,7 @@
         <v>0.1124656038762679</v>
       </c>
       <c r="M2" t="s">
-        <v>244</v>
+        <v>193</v>
       </c>
       <c r="N2">
         <v>-0.7258399112794024</v>
@@ -5565,19 +5254,19 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="F3">
         <v>106</v>
@@ -5586,13 +5275,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="I3" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="J3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="K3">
         <v>0.3083645129446252</v>
@@ -5601,7 +5290,7 @@
         <v>0.4111526839261669</v>
       </c>
       <c r="M3" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="N3">
         <v>0.918071182257265</v>
@@ -5618,19 +5307,19 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="E4" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="F4">
         <v>16</v>
@@ -5639,13 +5328,13 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="I4" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="J4" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="K4">
         <v>0.5166444797844136</v>
@@ -5654,7 +5343,7 @@
         <v>0.5166444797844136</v>
       </c>
       <c r="M4" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="N4">
         <v>-1.273695086711304</v>
@@ -5671,19 +5360,19 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D5" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="E5" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="F5">
         <v>54</v>
@@ -5692,13 +5381,13 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="I5" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="J5" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="K5">
         <v>0.09989191141023498</v>
@@ -5707,7 +5396,7 @@
         <v>0.19978382282047</v>
       </c>
       <c r="M5" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="N5">
         <v>1.283176345008311</v>
@@ -5724,19 +5413,19 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="E6" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="F6">
         <v>172</v>
@@ -5745,13 +5434,13 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="I6" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="J6" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="K6">
         <v>0.2056803019597374</v>
@@ -5760,7 +5449,7 @@
         <v>0.2742404026129832</v>
       </c>
       <c r="M6" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="N6">
         <v>-0.6958096544338495</v>
@@ -5777,19 +5466,19 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D7" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="E7" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="F7">
         <v>32</v>
@@ -5798,13 +5487,13 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="I7" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="J7" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="K7">
         <v>0.00205794964484609</v>
@@ -5813,7 +5502,7 @@
         <v>0.004359555799575449</v>
       </c>
       <c r="M7" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="N7">
         <v>1.191621191349772</v>
@@ -5830,19 +5519,19 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="E8" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="F8">
         <v>65</v>
@@ -5851,13 +5540,13 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="I8" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="J8" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="K8">
         <v>0.3170751160616128</v>
@@ -5866,7 +5555,7 @@
         <v>0.3170751160616128</v>
       </c>
       <c r="M8" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="N8">
         <v>-0.973285952397791</v>
@@ -5883,19 +5572,19 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D9" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="E9" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="F9">
         <v>19</v>
@@ -5904,13 +5593,13 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="I9" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="J9" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="K9">
         <v>0.002179777899787724</v>
@@ -5919,7 +5608,7 @@
         <v>0.004359555799575449</v>
       </c>
       <c r="M9" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="N9">
         <v>1.716849938307574</v>
@@ -5936,19 +5625,19 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="E10" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="F10">
         <v>34</v>
@@ -5957,13 +5646,13 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="I10" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="J10" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="K10">
         <v>0.3187619824129026</v>
@@ -5972,7 +5661,7 @@
         <v>0.4250159765505368</v>
       </c>
       <c r="M10" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="N10">
         <v>-0.633023201706413</v>
@@ -5989,19 +5678,19 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D11" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="E11" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="F11">
         <v>122</v>
@@ -6010,13 +5699,13 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="I11" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="J11" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="K11">
         <v>0.000768366270010823</v>
@@ -6025,7 +5714,7 @@
         <v>0.001536732540021646</v>
       </c>
       <c r="M11" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="N11">
         <v>0.5371813707305108</v>
@@ -6042,19 +5731,19 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="E12" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="F12">
         <v>14</v>
@@ -6063,13 +5752,13 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="I12" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="J12" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="K12">
         <v>0.5966613731568553</v>
@@ -6078,7 +5767,7 @@
         <v>0.5966613731568553</v>
       </c>
       <c r="M12" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="N12">
         <v>-1.044533156972018</v>
@@ -6095,19 +5784,19 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="E13" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="F13">
         <v>24</v>
@@ -6116,13 +5805,13 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="I13" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="J13" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="K13">
         <v>0.0005519921883541551</v>
@@ -6131,7 +5820,7 @@
         <v>0.001536732540021646</v>
       </c>
       <c r="M13" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="N13">
         <v>0.7737914310005581</v>
@@ -6148,19 +5837,19 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D14" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="E14" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="F14">
         <v>7</v>
@@ -6169,13 +5858,13 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="I14" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="J14" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="K14">
         <v>0.7391088073972578</v>
@@ -6184,7 +5873,7 @@
         <v>0.7391088073972578</v>
       </c>
       <c r="M14" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="N14">
         <v>-0.7111835336781603</v>
@@ -6201,19 +5890,19 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D15" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="E15" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="F15">
         <v>196</v>
@@ -6222,13 +5911,13 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="I15" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="J15" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="K15">
         <v>0.0151472518236927</v>
@@ -6237,7 +5926,7 @@
         <v>0.02272087773553904</v>
       </c>
       <c r="M15" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="N15">
         <v>0.574688710741055</v>
@@ -6254,19 +5943,19 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B16" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D16" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="E16" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -6275,30 +5964,30 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="I16" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D17" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="E17" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="F17">
         <v>48</v>
@@ -6307,13 +5996,13 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="I17" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="J17" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="K17">
         <v>0.005320244326701801</v>
@@ -6322,7 +6011,7 @@
         <v>0.0159607329801054</v>
       </c>
       <c r="M17" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="N17">
         <v>0.8503634914478839</v>
@@ -6349,57 +6038,57 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>199</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>200</v>
       </c>
       <c r="C3" t="s">
-        <v>252</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="C4" t="s">
-        <v>255</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>256</v>
+        <v>205</v>
       </c>
       <c r="B5" t="s">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -6414,585 +6103,585 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="C2" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>262</v>
+        <v>211</v>
       </c>
       <c r="B3" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="B4" t="s">
-        <v>265</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>266</v>
+        <v>215</v>
       </c>
       <c r="B5" t="s">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="C5" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="B6" t="s">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="C6" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>270</v>
+        <v>219</v>
       </c>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>272</v>
+        <v>221</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>222</v>
       </c>
       <c r="C8" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>274</v>
+        <v>223</v>
       </c>
       <c r="B9" t="s">
-        <v>275</v>
+        <v>224</v>
       </c>
       <c r="C9" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>276</v>
+        <v>225</v>
       </c>
       <c r="B10" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="C10" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="B11" t="s">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="C11" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>280</v>
+        <v>229</v>
       </c>
       <c r="B12" t="s">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="B13" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
       <c r="C13" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="B14" t="s">
-        <v>285</v>
+        <v>234</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="B15" t="s">
-        <v>287</v>
+        <v>236</v>
       </c>
       <c r="C15" t="s">
-        <v>288</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>289</v>
+        <v>238</v>
       </c>
       <c r="B16" t="s">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="B17" t="s">
-        <v>292</v>
+        <v>241</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>242</v>
       </c>
       <c r="B18" t="s">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="B19" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="C19" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="B20" t="s">
-        <v>298</v>
+        <v>247</v>
       </c>
       <c r="C20" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>299</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s">
-        <v>300</v>
+        <v>249</v>
       </c>
       <c r="C21" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>301</v>
+        <v>250</v>
       </c>
       <c r="B22" t="s">
-        <v>302</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>303</v>
+        <v>252</v>
       </c>
       <c r="B23" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="C23" t="s">
-        <v>288</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>305</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>307</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s">
-        <v>308</v>
+        <v>257</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>309</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s">
-        <v>310</v>
+        <v>259</v>
       </c>
       <c r="C26" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>311</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s">
-        <v>312</v>
+        <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>313</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s">
-        <v>314</v>
+        <v>263</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>315</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s">
-        <v>316</v>
+        <v>265</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s">
-        <v>318</v>
+        <v>267</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
       <c r="C31" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>321</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s">
-        <v>322</v>
+        <v>271</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s">
-        <v>324</v>
+        <v>273</v>
       </c>
       <c r="C33" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>325</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="C35" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s">
-        <v>330</v>
+        <v>279</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>331</v>
+        <v>280</v>
       </c>
       <c r="B37" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="C37" t="s">
-        <v>288</v>
+        <v>237</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s">
-        <v>334</v>
+        <v>283</v>
       </c>
       <c r="C38" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>335</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="B40" t="s">
-        <v>338</v>
+        <v>287</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>339</v>
+        <v>288</v>
       </c>
       <c r="B41" t="s">
-        <v>340</v>
+        <v>289</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>341</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s">
-        <v>342</v>
+        <v>291</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>343</v>
+        <v>292</v>
       </c>
       <c r="B43" t="s">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="B44" t="s">
-        <v>346</v>
+        <v>295</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>347</v>
+        <v>296</v>
       </c>
       <c r="B45" t="s">
-        <v>310</v>
+        <v>259</v>
       </c>
       <c r="C45" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="B46" t="s">
-        <v>275</v>
+        <v>224</v>
       </c>
       <c r="C46" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>349</v>
+        <v>298</v>
       </c>
       <c r="B47" t="s">
-        <v>350</v>
+        <v>299</v>
       </c>
       <c r="C47" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>351</v>
+        <v>300</v>
       </c>
       <c r="B48" t="s">
-        <v>352</v>
+        <v>301</v>
       </c>
       <c r="C48" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="B49" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="C49" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="B50" t="s">
-        <v>356</v>
+        <v>305</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>357</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s">
-        <v>358</v>
+        <v>307</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="B52" t="s">
-        <v>360</v>
+        <v>309</v>
       </c>
       <c r="C52" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>361</v>
+        <v>310</v>
       </c>
       <c r="B53" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="C53" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/04_Figures/F1/c_data/F1.xlsx
+++ b/04_Figures/F1/c_data/F1.xlsx
@@ -631,7 +631,7 @@
     <t>02_HRvLR/01_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>e706deccf806204996a968b97f852521</t>
+    <t>eb23e8a1866fdf41427417935863def8</t>
   </si>
   <si>
     <t>variance</t>
@@ -649,7 +649,7 @@
     <t>02_HRvLR/07_Group_Trait_Slopes/c_data/group_trait_slopes.xlsx</t>
   </si>
   <si>
-    <t>f24590e2277ed08b7470c1cb8b4f4eee</t>
+    <t>6dd01c4da2455f99b603e6b8b9827643</t>
   </si>
   <si>
     <t>BiocManager</t>

--- a/04_Figures/F1/c_data/F1.xlsx
+++ b/04_Figures/F1/c_data/F1.xlsx
@@ -640,7 +640,7 @@
     <t>02_HRvLR/04_Variance/c_data/variance.xlsx</t>
   </si>
   <si>
-    <t>21f4207236305a5ac8a5be8a5cbaf4be</t>
+    <t>844320d78318f2e845c02f6db890b83d</t>
   </si>
   <si>
     <t>slopes</t>
@@ -649,7 +649,7 @@
     <t>02_HRvLR/07_Group_Trait_Slopes/c_data/group_trait_slopes.xlsx</t>
   </si>
   <si>
-    <t>6dd01c4da2455f99b603e6b8b9827643</t>
+    <t>f24590e2277ed08b7470c1cb8b4f4eee</t>
   </si>
   <si>
     <t>BiocManager</t>

--- a/04_Figures/F1/c_data/F1.xlsx
+++ b/04_Figures/F1/c_data/F1.xlsx
@@ -13,16 +13,17 @@
     <sheet name="b_pca" sheetId="4" r:id="rId4"/>
     <sheet name="c_trait_effects" sheetId="5" r:id="rId5"/>
     <sheet name="d_counts" sheetId="6" r:id="rId6"/>
-    <sheet name="e_fry_transfer" sheetId="7" r:id="rId7"/>
-    <sheet name="input_manifest" sheetId="8" r:id="rId8"/>
-    <sheet name="package_versions" sheetId="9" r:id="rId9"/>
+    <sheet name="e_set_counts" sheetId="7" r:id="rId7"/>
+    <sheet name="f_fry_transfer" sheetId="8" r:id="rId8"/>
+    <sheet name="input_manifest" sheetId="9" r:id="rId9"/>
+    <sheet name="package_versions" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="321">
   <si>
     <t>sheet</t>
   </si>
@@ -60,10 +61,16 @@
     <t>Panel d: per contrast and direction, proteins at Π &lt; 0.05, p &lt; 0.05 and FDR &lt; 0.05.</t>
   </si>
   <si>
-    <t>e_fry_transfer</t>
-  </si>
-  <si>
-    <t>Panel e: each group's training and acute sets (Π or p &lt; 0.05) tested with fry in the other group's contrast; sets under 5 proteins were not tested.</t>
+    <t>e_set_counts</t>
+  </si>
+  <si>
+    <t>Panel e: per contrast and direction, gene sets at fgsea FDR &lt; 0.05 and sets tested.</t>
+  </si>
+  <si>
+    <t>f_fry_transfer</t>
+  </si>
+  <si>
+    <t>Panel f: each group's training and acute sets (Π or p &lt; 0.05) tested with fry in the other group's contrast; sets under 5 proteins were not tested.</t>
   </si>
   <si>
     <t>input_manifest</t>
@@ -319,6 +326,15 @@
   </si>
   <si>
     <t>Proteins expected at p &lt; 0.05 in one direction by chance: 2.5% of those tested.</t>
+  </si>
+  <si>
+    <t>Contrast family the row sits under: Training, Acute, Between groups or Interaction.</t>
+  </si>
+  <si>
+    <t>Gene sets tested in the contrast (Hallmark, Reactome, KEGG legacy, GO BP).</t>
+  </si>
+  <si>
+    <t>Gene sets at fgsea FDR &lt; 0.05 (within database) with NES in that direction.</t>
   </si>
   <si>
     <t>Window the set comes from: Training (T2 - T1) or Acute (T3 - T2).</t>
@@ -604,6 +620,9 @@
     <t>Training_Interaction</t>
   </si>
   <si>
+    <t>Between groups</t>
+  </si>
+  <si>
     <t>nominal</t>
   </si>
   <si>
@@ -650,6 +669,15 @@
   </si>
   <si>
     <t>f24590e2277ed08b7470c1cb8b4f4eee</t>
+  </si>
+  <si>
+    <t>set_tests</t>
+  </si>
+  <si>
+    <t>02_HRvLR/02_Set_Contrasts/c_data/set_tests.rds</t>
+  </si>
+  <si>
+    <t>30db8bea525624e038076e732efccd5f</t>
   </si>
   <si>
     <t>BiocManager</t>
@@ -1304,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -1377,6 +1405,607 @@
       </c>
       <c r="B9" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C53"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B13" t="s">
+        <v>241</v>
+      </c>
+      <c r="C13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>242</v>
+      </c>
+      <c r="B14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>244</v>
+      </c>
+      <c r="B15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C16" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>249</v>
+      </c>
+      <c r="B17" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B18" t="s">
+        <v>252</v>
+      </c>
+      <c r="C18" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>255</v>
+      </c>
+      <c r="B20" t="s">
+        <v>256</v>
+      </c>
+      <c r="C20" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>257</v>
+      </c>
+      <c r="B21" t="s">
+        <v>258</v>
+      </c>
+      <c r="C21" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>259</v>
+      </c>
+      <c r="B22" t="s">
+        <v>260</v>
+      </c>
+      <c r="C22" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>261</v>
+      </c>
+      <c r="B23" t="s">
+        <v>262</v>
+      </c>
+      <c r="C23" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>263</v>
+      </c>
+      <c r="B24" t="s">
+        <v>264</v>
+      </c>
+      <c r="C24" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>265</v>
+      </c>
+      <c r="B25" t="s">
+        <v>266</v>
+      </c>
+      <c r="C25" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>267</v>
+      </c>
+      <c r="B26" t="s">
+        <v>268</v>
+      </c>
+      <c r="C26" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>269</v>
+      </c>
+      <c r="B27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C27" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>271</v>
+      </c>
+      <c r="B28" t="s">
+        <v>272</v>
+      </c>
+      <c r="C28" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>273</v>
+      </c>
+      <c r="B29" t="s">
+        <v>274</v>
+      </c>
+      <c r="C29" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>275</v>
+      </c>
+      <c r="B30" t="s">
+        <v>276</v>
+      </c>
+      <c r="C30" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>277</v>
+      </c>
+      <c r="B31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C31" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>279</v>
+      </c>
+      <c r="B32" t="s">
+        <v>280</v>
+      </c>
+      <c r="C32" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>281</v>
+      </c>
+      <c r="B33" t="s">
+        <v>282</v>
+      </c>
+      <c r="C33" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>283</v>
+      </c>
+      <c r="B34" t="s">
+        <v>284</v>
+      </c>
+      <c r="C34" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>285</v>
+      </c>
+      <c r="B35" t="s">
+        <v>286</v>
+      </c>
+      <c r="C35" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>287</v>
+      </c>
+      <c r="B36" t="s">
+        <v>288</v>
+      </c>
+      <c r="C36" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>289</v>
+      </c>
+      <c r="B37" t="s">
+        <v>290</v>
+      </c>
+      <c r="C37" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>291</v>
+      </c>
+      <c r="B38" t="s">
+        <v>292</v>
+      </c>
+      <c r="C38" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>293</v>
+      </c>
+      <c r="B39" t="s">
+        <v>294</v>
+      </c>
+      <c r="C39" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>295</v>
+      </c>
+      <c r="B40" t="s">
+        <v>296</v>
+      </c>
+      <c r="C40" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>297</v>
+      </c>
+      <c r="B41" t="s">
+        <v>298</v>
+      </c>
+      <c r="C41" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>299</v>
+      </c>
+      <c r="B42" t="s">
+        <v>300</v>
+      </c>
+      <c r="C42" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>301</v>
+      </c>
+      <c r="B43" t="s">
+        <v>302</v>
+      </c>
+      <c r="C43" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>303</v>
+      </c>
+      <c r="B44" t="s">
+        <v>304</v>
+      </c>
+      <c r="C44" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>305</v>
+      </c>
+      <c r="B45" t="s">
+        <v>268</v>
+      </c>
+      <c r="C45" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>306</v>
+      </c>
+      <c r="B46" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>307</v>
+      </c>
+      <c r="B47" t="s">
+        <v>308</v>
+      </c>
+      <c r="C47" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>309</v>
+      </c>
+      <c r="B48" t="s">
+        <v>310</v>
+      </c>
+      <c r="C48" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>311</v>
+      </c>
+      <c r="B49" t="s">
+        <v>312</v>
+      </c>
+      <c r="C49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>313</v>
+      </c>
+      <c r="B50" t="s">
+        <v>314</v>
+      </c>
+      <c r="C50" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>315</v>
+      </c>
+      <c r="B51" t="s">
+        <v>316</v>
+      </c>
+      <c r="C51" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>317</v>
+      </c>
+      <c r="B52" t="s">
+        <v>318</v>
+      </c>
+      <c r="C52" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>319</v>
+      </c>
+      <c r="B53" t="s">
+        <v>320</v>
+      </c>
+      <c r="C53" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -1386,7 +2015,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -1394,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1405,10 +2034,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1416,10 +2045,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1427,10 +2056,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1438,10 +2067,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1449,10 +2078,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1460,10 +2089,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1471,10 +2100,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1482,10 +2111,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1493,10 +2122,10 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1504,10 +2133,10 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1515,10 +2144,10 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1526,10 +2155,10 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1537,10 +2166,10 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1548,10 +2177,10 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1559,10 +2188,10 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1570,10 +2199,10 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1581,10 +2210,10 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1592,10 +2221,10 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1603,10 +2232,10 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1614,10 +2243,10 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1625,10 +2254,10 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1636,10 +2265,10 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1647,10 +2276,10 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1658,10 +2287,10 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1669,10 +2298,10 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1680,10 +2309,10 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1691,10 +2320,10 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1702,10 +2331,10 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1713,10 +2342,10 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1724,10 +2353,10 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1735,10 +2364,10 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1746,10 +2375,10 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1757,10 +2386,10 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1768,10 +2397,10 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1779,10 +2408,10 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1790,10 +2419,10 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1801,10 +2430,10 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1812,10 +2441,10 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1823,10 +2452,10 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1834,10 +2463,10 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1845,10 +2474,10 @@
         <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1856,10 +2485,10 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1867,10 +2496,10 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1878,10 +2507,10 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1889,10 +2518,10 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1900,10 +2529,10 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1911,131 +2540,131 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C48" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C57" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C58" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="C59" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -2043,10 +2672,10 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C60" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -2054,10 +2683,10 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2065,43 +2694,109 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C63" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C64" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
         <v>16</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B66" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>16</v>
+      </c>
+      <c r="B67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68" t="s">
+        <v>138</v>
+      </c>
+      <c r="C68" t="s">
         <v>139</v>
       </c>
-      <c r="C65" t="s">
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69" t="s">
         <v>140</v>
+      </c>
+      <c r="C69" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70" t="s">
+        <v>142</v>
+      </c>
+      <c r="C70" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71" t="s">
+        <v>144</v>
+      </c>
+      <c r="C71" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2116,25 +2811,25 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2151,7 +2846,7 @@
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F2">
         <v>5488</v>
@@ -2172,51 +2867,51 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D2">
         <v>-29.03668837129199</v>
@@ -2248,13 +2943,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D3">
         <v>14.52182560559677</v>
@@ -2286,13 +2981,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D4">
         <v>6.347878895134587</v>
@@ -2324,13 +3019,13 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D5">
         <v>-40.40482862456631</v>
@@ -2362,13 +3057,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D6">
         <v>10.45489006361174</v>
@@ -2400,13 +3095,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" t="s">
         <v>149</v>
-      </c>
-      <c r="C7" t="s">
-        <v>144</v>
       </c>
       <c r="D7">
         <v>-1.132590706856136</v>
@@ -2438,13 +3133,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D8">
         <v>20.46158158979756</v>
@@ -2476,13 +3171,13 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D9">
         <v>3.289723066035478</v>
@@ -2514,13 +3209,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D10">
         <v>13.08056937520334</v>
@@ -2552,13 +3247,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D11">
         <v>20.60276149624735</v>
@@ -2590,13 +3285,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D12">
         <v>11.4309992200542</v>
@@ -2628,13 +3323,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D13">
         <v>7.603404674660928</v>
@@ -2666,13 +3361,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B14" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D14">
         <v>-1.815703959054005</v>
@@ -2704,13 +3399,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" t="s">
         <v>158</v>
-      </c>
-      <c r="C15" t="s">
-        <v>153</v>
       </c>
       <c r="D15">
         <v>-24.79211528765926</v>
@@ -2742,13 +3437,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B16" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C16" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D16">
         <v>-0.2726434558318989</v>
@@ -2780,13 +3475,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B17" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D17">
         <v>-10.33906358108228</v>
@@ -2818,13 +3513,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D18">
         <v>-21.45268611886402</v>
@@ -2856,13 +3551,13 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D19">
         <v>30.65620820961616</v>
@@ -2894,13 +3589,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D20">
         <v>-13.13268726403322</v>
@@ -2932,13 +3627,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B21" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D21">
         <v>-21.13657678120648</v>
@@ -2970,13 +3665,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D22">
         <v>14.98295857510104</v>
@@ -3008,13 +3703,13 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" t="s">
         <v>149</v>
-      </c>
-      <c r="C23" t="s">
-        <v>144</v>
       </c>
       <c r="D23">
         <v>-10.77856494084534</v>
@@ -3046,13 +3741,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D24">
         <v>61.46580929732519</v>
@@ -3084,13 +3779,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D25">
         <v>-6.582695963512122</v>
@@ -3122,13 +3817,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B26" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D26">
         <v>-10.49403302399655</v>
@@ -3160,13 +3855,13 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C27" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D27">
         <v>-0.8520404240935795</v>
@@ -3198,13 +3893,13 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D28">
         <v>-8.905161704142964</v>
@@ -3236,13 +3931,13 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" t="s">
         <v>161</v>
       </c>
-      <c r="B29" t="s">
-        <v>156</v>
-      </c>
       <c r="C29" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D29">
         <v>3.673624967765215</v>
@@ -3274,13 +3969,13 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C30" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D30">
         <v>-7.780695865248901</v>
@@ -3312,13 +4007,13 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C31" t="s">
         <v>158</v>
-      </c>
-      <c r="C31" t="s">
-        <v>153</v>
       </c>
       <c r="D31">
         <v>3.66485814620185</v>
@@ -3350,13 +4045,13 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D32">
         <v>-3.654005474511882</v>
@@ -3388,13 +4083,13 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D33">
         <v>-9.674311635554265</v>
@@ -3426,13 +4121,13 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B34" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D34">
         <v>-14.11432723695496</v>
@@ -3464,13 +4159,13 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D35">
         <v>-50.63670537156404</v>
@@ -3502,13 +4197,13 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C36" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D36">
         <v>6.996138059323121</v>
@@ -3540,13 +4235,13 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D37">
         <v>-0.6500778682620784</v>
@@ -3578,13 +4273,13 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D38">
         <v>-45.10179677976108</v>
@@ -3616,13 +4311,13 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" t="s">
         <v>149</v>
-      </c>
-      <c r="C39" t="s">
-        <v>144</v>
       </c>
       <c r="D39">
         <v>19.10707537583495</v>
@@ -3654,13 +4349,13 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D40">
         <v>1.675538076477031</v>
@@ -3692,13 +4387,13 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B41" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C41" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D41">
         <v>20.84566414077102</v>
@@ -3730,13 +4425,13 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D42">
         <v>11.13885990877638</v>
@@ -3768,13 +4463,13 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D43">
         <v>18.81592132947557</v>
@@ -3806,13 +4501,13 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D44">
         <v>5.333622346347253</v>
@@ -3844,13 +4539,13 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D45">
         <v>8.916715707470596</v>
@@ -3882,13 +4577,13 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" t="s">
         <v>162</v>
       </c>
-      <c r="B46" t="s">
-        <v>157</v>
-      </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D46">
         <v>5.027703058812455</v>
@@ -3920,13 +4615,13 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B47" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" t="s">
         <v>158</v>
-      </c>
-      <c r="C47" t="s">
-        <v>153</v>
       </c>
       <c r="D47">
         <v>-6.877154736840926</v>
@@ -3958,13 +4653,13 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D48">
         <v>13.61621960807793</v>
@@ -3996,13 +4691,13 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D49">
         <v>5.906604382016643</v>
@@ -4044,54 +4739,54 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -4115,10 +4810,10 @@
         <v>0.001713171134239212</v>
       </c>
       <c r="K2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="L2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -4126,13 +4821,13 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D3">
         <v>8</v>
@@ -4156,10 +4851,10 @@
         <v>0.001713171134239212</v>
       </c>
       <c r="K3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="L3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -4167,13 +4862,13 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -4197,10 +4892,10 @@
         <v>0.01023059163043604</v>
       </c>
       <c r="K4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="L4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
@@ -4208,13 +4903,13 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -4238,10 +4933,10 @@
         <v>0.01023059163043604</v>
       </c>
       <c r="K5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="L5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -4249,13 +4944,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B6" t="b">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -4279,10 +4974,10 @@
         <v>0.002763676599144667</v>
       </c>
       <c r="K6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L6" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -4290,13 +4985,13 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B7" t="b">
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -4320,10 +5015,10 @@
         <v>0.002763676599144667</v>
       </c>
       <c r="K7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -4331,13 +5026,13 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B8" t="b">
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D8">
         <v>8</v>
@@ -4361,10 +5056,10 @@
         <v>0.00100838258081328</v>
       </c>
       <c r="K8" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -4372,13 +5067,13 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B9" t="b">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -4402,10 +5097,10 @@
         <v>0.00100838258081328</v>
       </c>
       <c r="K9" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L9" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -4413,13 +5108,13 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B10" t="b">
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -4443,10 +5138,10 @@
         <v>0.8464533285112503</v>
       </c>
       <c r="K10" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L10" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="M10" t="b">
         <v>1</v>
@@ -4454,13 +5149,13 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B11" t="b">
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -4484,10 +5179,10 @@
         <v>0.8464533285112503</v>
       </c>
       <c r="K11" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L11" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="M11" t="b">
         <v>1</v>
@@ -4495,13 +5190,13 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B12" t="b">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -4525,10 +5220,10 @@
         <v>0.4262518511068021</v>
       </c>
       <c r="K12" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L12" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="M12" t="b">
         <v>1</v>
@@ -4536,13 +5231,13 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B13" t="b">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -4566,10 +5261,10 @@
         <v>0.4262518511068021</v>
       </c>
       <c r="K13" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L13" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
@@ -4587,45 +5282,45 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E2">
         <v>2059</v>
@@ -4645,16 +5340,16 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E3">
         <v>2059</v>
@@ -4674,16 +5369,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E4">
         <v>2059</v>
@@ -4703,16 +5398,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E5">
         <v>2059</v>
@@ -4732,16 +5427,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E6">
         <v>2059</v>
@@ -4761,16 +5456,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D7" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E7">
         <v>2059</v>
@@ -4790,16 +5485,16 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E8">
         <v>2059</v>
@@ -4819,16 +5514,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E9">
         <v>2059</v>
@@ -4848,16 +5543,16 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" t="s">
         <v>183</v>
-      </c>
-      <c r="B10" t="s">
-        <v>184</v>
-      </c>
-      <c r="C10" t="s">
-        <v>185</v>
-      </c>
-      <c r="D10" t="s">
-        <v>178</v>
       </c>
       <c r="E10">
         <v>2059</v>
@@ -4877,16 +5572,16 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" t="s">
         <v>184</v>
-      </c>
-      <c r="C11" t="s">
-        <v>185</v>
-      </c>
-      <c r="D11" t="s">
-        <v>179</v>
       </c>
       <c r="E11">
         <v>2059</v>
@@ -4906,16 +5601,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D12" t="s">
         <v>183</v>
-      </c>
-      <c r="B12" t="s">
-        <v>142</v>
-      </c>
-      <c r="C12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D12" t="s">
-        <v>178</v>
       </c>
       <c r="E12">
         <v>2059</v>
@@ -4935,16 +5630,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D13" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E13">
         <v>2059</v>
@@ -4964,16 +5659,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D14" t="s">
         <v>183</v>
-      </c>
-      <c r="B14" t="s">
-        <v>187</v>
-      </c>
-      <c r="C14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D14" t="s">
-        <v>178</v>
       </c>
       <c r="E14">
         <v>2059</v>
@@ -4993,16 +5688,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D15" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E15">
         <v>2059</v>
@@ -5022,16 +5717,16 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C16" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D16" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E16">
         <v>2059</v>
@@ -5051,16 +5746,16 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C17" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D17" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E17">
         <v>2059</v>
@@ -5080,16 +5775,16 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D18" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E18">
         <v>2059</v>
@@ -5109,16 +5804,16 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D19" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E19">
         <v>2059</v>
@@ -5143,887 +5838,387 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2">
+        <v>1364</v>
+      </c>
+      <c r="F2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3">
+        <v>1364</v>
+      </c>
+      <c r="F3">
         <v>70</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F2">
-        <v>49</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I2" t="s">
-        <v>182</v>
-      </c>
-      <c r="J2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K2">
-        <v>0.02811640096906698</v>
-      </c>
-      <c r="L2">
-        <v>0.1124656038762679</v>
-      </c>
-      <c r="M2" t="s">
-        <v>193</v>
-      </c>
-      <c r="N2">
-        <v>-0.7258399112794024</v>
-      </c>
-      <c r="O2">
-        <v>-0.1551216800512224</v>
-      </c>
-      <c r="P2">
-        <v>0.7755102040816326</v>
-      </c>
-      <c r="Q2">
-        <v>-1.551040271821073</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F3">
-        <v>106</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K3">
-        <v>0.3083645129446252</v>
-      </c>
-      <c r="L3">
-        <v>0.4111526839261669</v>
-      </c>
-      <c r="M3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N3">
-        <v>0.918071182257265</v>
-      </c>
-      <c r="O3">
-        <v>0.2784657250072696</v>
-      </c>
-      <c r="P3">
-        <v>0.6320754716981132</v>
-      </c>
-      <c r="Q3">
-        <v>0.5109356070124644</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E4" t="s">
-        <v>179</v>
+        <v>183</v>
+      </c>
+      <c r="E4">
+        <v>1364</v>
       </c>
       <c r="F4">
         <v>16</v>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I4" t="s">
-        <v>182</v>
-      </c>
-      <c r="J4" t="s">
-        <v>179</v>
-      </c>
-      <c r="K4">
-        <v>0.5166444797844136</v>
-      </c>
-      <c r="L4">
-        <v>0.5166444797844136</v>
-      </c>
-      <c r="M4" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5">
+        <v>1364</v>
+      </c>
+      <c r="F5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6">
+        <v>1364</v>
+      </c>
+      <c r="F6">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7">
+        <v>1364</v>
+      </c>
+      <c r="F7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8">
+        <v>1364</v>
+      </c>
+      <c r="F8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9">
+        <v>1364</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10">
+        <v>1364</v>
+      </c>
+      <c r="F10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11">
+        <v>1364</v>
+      </c>
+      <c r="F11">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12">
+        <v>1364</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13">
+        <v>1364</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14">
+        <v>1364</v>
+      </c>
+      <c r="F14">
         <v>194</v>
       </c>
-      <c r="N4">
-        <v>-1.273695086711304</v>
-      </c>
-      <c r="O4">
-        <v>-0.01097168334189445</v>
-      </c>
-      <c r="P4">
-        <v>0.625</v>
-      </c>
-      <c r="Q4">
-        <v>-0.2868082065766502</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15">
+        <v>1364</v>
+      </c>
+      <c r="F15">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16">
+        <v>1364</v>
+      </c>
+      <c r="F16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17">
+        <v>1364</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" t="s">
         <v>195</v>
       </c>
-      <c r="E5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F5">
-        <v>54</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I5" t="s">
-        <v>182</v>
-      </c>
-      <c r="J5" t="s">
-        <v>178</v>
-      </c>
-      <c r="K5">
-        <v>0.09989191141023498</v>
-      </c>
-      <c r="L5">
-        <v>0.19978382282047</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="D18" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18">
+        <v>1364</v>
+      </c>
+      <c r="F18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
         <v>194</v>
       </c>
-      <c r="N5">
-        <v>1.283176345008311</v>
-      </c>
-      <c r="O5">
-        <v>0.51021220914251</v>
-      </c>
-      <c r="P5">
-        <v>0.7592592592592593</v>
-      </c>
-      <c r="Q5">
-        <v>1.000469676660108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6">
-        <v>172</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>182</v>
-      </c>
-      <c r="I6" t="s">
-        <v>181</v>
-      </c>
-      <c r="J6" t="s">
-        <v>179</v>
-      </c>
-      <c r="K6">
-        <v>0.2056803019597374</v>
-      </c>
-      <c r="L6">
-        <v>0.2742404026129832</v>
-      </c>
-      <c r="M6" t="s">
-        <v>194</v>
-      </c>
-      <c r="N6">
-        <v>-0.6958096544338495</v>
-      </c>
-      <c r="O6">
-        <v>-0.1159811897425118</v>
-      </c>
-      <c r="P6">
-        <v>0.7034883720930233</v>
-      </c>
-      <c r="Q6">
-        <v>-0.6868072987759725</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E7" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7">
-        <v>32</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>182</v>
-      </c>
-      <c r="I7" t="s">
-        <v>181</v>
-      </c>
-      <c r="J7" t="s">
-        <v>178</v>
-      </c>
-      <c r="K7">
-        <v>0.00205794964484609</v>
-      </c>
-      <c r="L7">
-        <v>0.004359555799575449</v>
-      </c>
-      <c r="M7" t="s">
-        <v>196</v>
-      </c>
-      <c r="N7">
-        <v>1.191621191349772</v>
-      </c>
-      <c r="O7">
-        <v>0.8086899578323585</v>
-      </c>
-      <c r="P7">
-        <v>0.875</v>
-      </c>
-      <c r="Q7">
-        <v>2.686565256023065</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" t="s">
         <v>195</v>
       </c>
-      <c r="E8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F8">
-        <v>65</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>182</v>
-      </c>
-      <c r="I8" t="s">
-        <v>181</v>
-      </c>
-      <c r="J8" t="s">
-        <v>179</v>
-      </c>
-      <c r="K8">
-        <v>0.3170751160616128</v>
-      </c>
-      <c r="L8">
-        <v>0.3170751160616128</v>
-      </c>
-      <c r="M8" t="s">
-        <v>194</v>
-      </c>
-      <c r="N8">
-        <v>-0.973285952397791</v>
-      </c>
-      <c r="O8">
-        <v>-0.1301074378981521</v>
-      </c>
-      <c r="P8">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="Q8">
-        <v>-0.4988378399066278</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" t="s">
-        <v>178</v>
-      </c>
-      <c r="F9">
-        <v>19</v>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="s">
-        <v>182</v>
-      </c>
-      <c r="I9" t="s">
-        <v>181</v>
-      </c>
-      <c r="J9" t="s">
-        <v>178</v>
-      </c>
-      <c r="K9">
-        <v>0.002179777899787724</v>
-      </c>
-      <c r="L9">
-        <v>0.004359555799575449</v>
-      </c>
-      <c r="M9" t="s">
-        <v>196</v>
-      </c>
-      <c r="N9">
-        <v>1.716849938307574</v>
-      </c>
-      <c r="O9">
-        <v>1.109424334064693</v>
-      </c>
-      <c r="P9">
-        <v>0.8947368421052632</v>
-      </c>
-      <c r="Q9">
-        <v>2.661587754932326</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" t="s">
-        <v>153</v>
-      </c>
-      <c r="D10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10">
-        <v>34</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="s">
-        <v>177</v>
-      </c>
-      <c r="I10" t="s">
-        <v>180</v>
-      </c>
-      <c r="J10" t="s">
-        <v>179</v>
-      </c>
-      <c r="K10">
-        <v>0.3187619824129026</v>
-      </c>
-      <c r="L10">
-        <v>0.4250159765505368</v>
-      </c>
-      <c r="M10" t="s">
-        <v>194</v>
-      </c>
-      <c r="N10">
-        <v>-0.633023201706413</v>
-      </c>
-      <c r="O10">
-        <v>-0.09019867659319955</v>
-      </c>
-      <c r="P10">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="Q10">
-        <v>-0.4965334809172235</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B11" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" t="s">
-        <v>153</v>
-      </c>
-      <c r="D11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" t="s">
-        <v>178</v>
-      </c>
-      <c r="F11">
-        <v>122</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>177</v>
-      </c>
-      <c r="I11" t="s">
-        <v>180</v>
-      </c>
-      <c r="J11" t="s">
-        <v>178</v>
-      </c>
-      <c r="K11">
-        <v>0.000768366270010823</v>
-      </c>
-      <c r="L11">
-        <v>0.001536732540021646</v>
-      </c>
-      <c r="M11" t="s">
-        <v>196</v>
-      </c>
-      <c r="N11">
-        <v>0.5371813707305108</v>
-      </c>
-      <c r="O11">
-        <v>0.2950199217909802</v>
-      </c>
-      <c r="P11">
-        <v>0.9180327868852459</v>
-      </c>
-      <c r="Q11">
-        <v>3.114431708190481</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" t="s">
-        <v>153</v>
-      </c>
-      <c r="D12" t="s">
-        <v>195</v>
-      </c>
-      <c r="E12" t="s">
-        <v>179</v>
-      </c>
-      <c r="F12">
-        <v>14</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>177</v>
-      </c>
-      <c r="I12" t="s">
-        <v>180</v>
-      </c>
-      <c r="J12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K12">
-        <v>0.5966613731568553</v>
-      </c>
-      <c r="L12">
-        <v>0.5966613731568553</v>
-      </c>
-      <c r="M12" t="s">
-        <v>194</v>
-      </c>
-      <c r="N12">
-        <v>-1.044533156972018</v>
-      </c>
-      <c r="O12">
-        <v>-0.1982404704985165</v>
-      </c>
-      <c r="P12">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="Q12">
-        <v>-0.224272076732449</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13" t="s">
-        <v>144</v>
-      </c>
-      <c r="C13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E13" t="s">
-        <v>178</v>
-      </c>
-      <c r="F13">
-        <v>24</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>177</v>
-      </c>
-      <c r="I13" t="s">
-        <v>180</v>
-      </c>
-      <c r="J13" t="s">
-        <v>178</v>
-      </c>
-      <c r="K13">
-        <v>0.0005519921883541551</v>
-      </c>
-      <c r="L13">
-        <v>0.001536732540021646</v>
-      </c>
-      <c r="M13" t="s">
-        <v>196</v>
-      </c>
-      <c r="N13">
-        <v>0.7737914310005581</v>
-      </c>
-      <c r="O13">
-        <v>0.4023095300919867</v>
-      </c>
-      <c r="P13">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="Q13">
-        <v>3.258067068246689</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" t="s">
-        <v>161</v>
-      </c>
-      <c r="B14" t="s">
-        <v>153</v>
-      </c>
-      <c r="C14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" t="s">
-        <v>192</v>
-      </c>
-      <c r="E14" t="s">
-        <v>179</v>
-      </c>
-      <c r="F14">
-        <v>7</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>180</v>
-      </c>
-      <c r="I14" t="s">
-        <v>177</v>
-      </c>
-      <c r="J14" t="s">
-        <v>179</v>
-      </c>
-      <c r="K14">
-        <v>0.7391088073972578</v>
-      </c>
-      <c r="L14">
-        <v>0.7391088073972578</v>
-      </c>
-      <c r="M14" t="s">
-        <v>194</v>
-      </c>
-      <c r="N14">
-        <v>-0.7111835336781603</v>
-      </c>
-      <c r="O14">
-        <v>-0.01369609822375014</v>
-      </c>
-      <c r="P14">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="Q14">
-        <v>-0.1312916225337498</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D15" t="s">
-        <v>192</v>
-      </c>
-      <c r="E15" t="s">
-        <v>178</v>
-      </c>
-      <c r="F15">
-        <v>196</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>180</v>
-      </c>
-      <c r="I15" t="s">
-        <v>177</v>
-      </c>
-      <c r="J15" t="s">
-        <v>178</v>
-      </c>
-      <c r="K15">
-        <v>0.0151472518236927</v>
-      </c>
-      <c r="L15">
-        <v>0.02272087773553904</v>
-      </c>
-      <c r="M15" t="s">
-        <v>196</v>
-      </c>
-      <c r="N15">
-        <v>0.574688710741055</v>
-      </c>
-      <c r="O15">
-        <v>0.1744719349694764</v>
-      </c>
-      <c r="P15">
-        <v>0.7448979591836735</v>
-      </c>
-      <c r="Q15">
-        <v>1.819666154360976</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" t="s">
-        <v>195</v>
-      </c>
-      <c r="E16" t="s">
-        <v>179</v>
-      </c>
-      <c r="F16">
-        <v>3</v>
-      </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>180</v>
-      </c>
-      <c r="I16" t="s">
-        <v>177</v>
-      </c>
-      <c r="M16" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B17" t="s">
-        <v>153</v>
-      </c>
-      <c r="C17" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" t="s">
-        <v>195</v>
-      </c>
-      <c r="E17" t="s">
-        <v>178</v>
-      </c>
-      <c r="F17">
-        <v>48</v>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="s">
-        <v>180</v>
-      </c>
-      <c r="I17" t="s">
-        <v>177</v>
-      </c>
-      <c r="J17" t="s">
-        <v>178</v>
-      </c>
-      <c r="K17">
-        <v>0.005320244326701801</v>
-      </c>
-      <c r="L17">
-        <v>0.0159607329801054</v>
-      </c>
-      <c r="M17" t="s">
-        <v>196</v>
-      </c>
-      <c r="N17">
-        <v>0.8503634914478839</v>
-      </c>
-      <c r="O17">
-        <v>0.238967985783441</v>
-      </c>
-      <c r="P17">
-        <v>0.75</v>
-      </c>
-      <c r="Q17">
-        <v>2.274068422723402</v>
+      <c r="D19" t="s">
+        <v>184</v>
+      </c>
+      <c r="E19">
+        <v>1364</v>
+      </c>
+      <c r="F19">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -6033,62 +6228,887 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1">
+    <row r="1" spans="1:17" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>107</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="E2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2">
+        <v>49</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K2">
+        <v>0.02811640096906698</v>
+      </c>
+      <c r="L2">
+        <v>0.1124656038762679</v>
+      </c>
+      <c r="M2" t="s">
+        <v>199</v>
+      </c>
+      <c r="N2">
+        <v>-0.7258399112794024</v>
+      </c>
+      <c r="O2">
+        <v>-0.1551216800512224</v>
+      </c>
+      <c r="P2">
+        <v>0.7755102040816326</v>
+      </c>
+      <c r="Q2">
+        <v>-1.551040271821073</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3">
+        <v>106</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K3">
+        <v>0.3083645129446252</v>
+      </c>
+      <c r="L3">
+        <v>0.4111526839261669</v>
+      </c>
+      <c r="M3" t="s">
         <v>200</v>
       </c>
-      <c r="C3" t="s">
+      <c r="N3">
+        <v>0.918071182257265</v>
+      </c>
+      <c r="O3">
+        <v>0.2784657250072696</v>
+      </c>
+      <c r="P3">
+        <v>0.6320754716981132</v>
+      </c>
+      <c r="Q3">
+        <v>0.5109356070124644</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="E4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4">
+        <v>16</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K4">
+        <v>0.5166444797844136</v>
+      </c>
+      <c r="L4">
+        <v>0.5166444797844136</v>
+      </c>
+      <c r="M4" t="s">
+        <v>200</v>
+      </c>
+      <c r="N4">
+        <v>-1.273695086711304</v>
+      </c>
+      <c r="O4">
+        <v>-0.01097168334189445</v>
+      </c>
+      <c r="P4">
+        <v>0.625</v>
+      </c>
+      <c r="Q4">
+        <v>-0.2868082065766502</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F5">
+        <v>54</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" t="s">
+        <v>187</v>
+      </c>
+      <c r="J5" t="s">
+        <v>183</v>
+      </c>
+      <c r="K5">
+        <v>0.09989191141023498</v>
+      </c>
+      <c r="L5">
+        <v>0.19978382282047</v>
+      </c>
+      <c r="M5" t="s">
+        <v>200</v>
+      </c>
+      <c r="N5">
+        <v>1.283176345008311</v>
+      </c>
+      <c r="O5">
+        <v>0.51021220914251</v>
+      </c>
+      <c r="P5">
+        <v>0.7592592592592593</v>
+      </c>
+      <c r="Q5">
+        <v>1.000469676660108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6">
+        <v>172</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I6" t="s">
+        <v>186</v>
+      </c>
+      <c r="J6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K6">
+        <v>0.2056803019597374</v>
+      </c>
+      <c r="L6">
+        <v>0.2742404026129832</v>
+      </c>
+      <c r="M6" t="s">
+        <v>200</v>
+      </c>
+      <c r="N6">
+        <v>-0.6958096544338495</v>
+      </c>
+      <c r="O6">
+        <v>-0.1159811897425118</v>
+      </c>
+      <c r="P6">
+        <v>0.7034883720930233</v>
+      </c>
+      <c r="Q6">
+        <v>-0.6868072987759725</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7">
+        <v>32</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" t="s">
+        <v>186</v>
+      </c>
+      <c r="J7" t="s">
+        <v>183</v>
+      </c>
+      <c r="K7">
+        <v>0.00205794964484609</v>
+      </c>
+      <c r="L7">
+        <v>0.004359555799575449</v>
+      </c>
+      <c r="M7" t="s">
         <v>202</v>
       </c>
-      <c r="B4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C5" t="s">
-        <v>207</v>
+      <c r="N7">
+        <v>1.191621191349772</v>
+      </c>
+      <c r="O7">
+        <v>0.8086899578323585</v>
+      </c>
+      <c r="P7">
+        <v>0.875</v>
+      </c>
+      <c r="Q7">
+        <v>2.686565256023065</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8">
+        <v>65</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>187</v>
+      </c>
+      <c r="I8" t="s">
+        <v>186</v>
+      </c>
+      <c r="J8" t="s">
+        <v>184</v>
+      </c>
+      <c r="K8">
+        <v>0.3170751160616128</v>
+      </c>
+      <c r="L8">
+        <v>0.3170751160616128</v>
+      </c>
+      <c r="M8" t="s">
+        <v>200</v>
+      </c>
+      <c r="N8">
+        <v>-0.973285952397791</v>
+      </c>
+      <c r="O8">
+        <v>-0.1301074378981521</v>
+      </c>
+      <c r="P8">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="Q8">
+        <v>-0.4988378399066278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F9">
+        <v>19</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>187</v>
+      </c>
+      <c r="I9" t="s">
+        <v>186</v>
+      </c>
+      <c r="J9" t="s">
+        <v>183</v>
+      </c>
+      <c r="K9">
+        <v>0.002179777899787724</v>
+      </c>
+      <c r="L9">
+        <v>0.004359555799575449</v>
+      </c>
+      <c r="M9" t="s">
+        <v>202</v>
+      </c>
+      <c r="N9">
+        <v>1.716849938307574</v>
+      </c>
+      <c r="O9">
+        <v>1.109424334064693</v>
+      </c>
+      <c r="P9">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="Q9">
+        <v>2.661587754932326</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F10">
+        <v>34</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I10" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" t="s">
+        <v>184</v>
+      </c>
+      <c r="K10">
+        <v>0.3187619824129026</v>
+      </c>
+      <c r="L10">
+        <v>0.4250159765505368</v>
+      </c>
+      <c r="M10" t="s">
+        <v>200</v>
+      </c>
+      <c r="N10">
+        <v>-0.633023201706413</v>
+      </c>
+      <c r="O10">
+        <v>-0.09019867659319955</v>
+      </c>
+      <c r="P10">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="Q10">
+        <v>-0.4965334809172235</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11">
+        <v>122</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>182</v>
+      </c>
+      <c r="I11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J11" t="s">
+        <v>183</v>
+      </c>
+      <c r="K11">
+        <v>0.000768366270010823</v>
+      </c>
+      <c r="L11">
+        <v>0.001536732540021646</v>
+      </c>
+      <c r="M11" t="s">
+        <v>202</v>
+      </c>
+      <c r="N11">
+        <v>0.5371813707305108</v>
+      </c>
+      <c r="O11">
+        <v>0.2950199217909802</v>
+      </c>
+      <c r="P11">
+        <v>0.9180327868852459</v>
+      </c>
+      <c r="Q11">
+        <v>3.114431708190481</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12">
+        <v>14</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>182</v>
+      </c>
+      <c r="I12" t="s">
+        <v>185</v>
+      </c>
+      <c r="J12" t="s">
+        <v>184</v>
+      </c>
+      <c r="K12">
+        <v>0.5966613731568553</v>
+      </c>
+      <c r="L12">
+        <v>0.5966613731568553</v>
+      </c>
+      <c r="M12" t="s">
+        <v>200</v>
+      </c>
+      <c r="N12">
+        <v>-1.044533156972018</v>
+      </c>
+      <c r="O12">
+        <v>-0.1982404704985165</v>
+      </c>
+      <c r="P12">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="Q12">
+        <v>-0.224272076732449</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13">
+        <v>24</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I13" t="s">
+        <v>185</v>
+      </c>
+      <c r="J13" t="s">
+        <v>183</v>
+      </c>
+      <c r="K13">
+        <v>0.0005519921883541551</v>
+      </c>
+      <c r="L13">
+        <v>0.001536732540021646</v>
+      </c>
+      <c r="M13" t="s">
+        <v>202</v>
+      </c>
+      <c r="N13">
+        <v>0.7737914310005581</v>
+      </c>
+      <c r="O13">
+        <v>0.4023095300919867</v>
+      </c>
+      <c r="P13">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="Q13">
+        <v>3.258067068246689</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" t="s">
+        <v>198</v>
+      </c>
+      <c r="E14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>185</v>
+      </c>
+      <c r="I14" t="s">
+        <v>182</v>
+      </c>
+      <c r="J14" t="s">
+        <v>184</v>
+      </c>
+      <c r="K14">
+        <v>0.7391088073972578</v>
+      </c>
+      <c r="L14">
+        <v>0.7391088073972578</v>
+      </c>
+      <c r="M14" t="s">
+        <v>200</v>
+      </c>
+      <c r="N14">
+        <v>-0.7111835336781603</v>
+      </c>
+      <c r="O14">
+        <v>-0.01369609822375014</v>
+      </c>
+      <c r="P14">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Q14">
+        <v>-0.1312916225337498</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D15" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15">
+        <v>196</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>185</v>
+      </c>
+      <c r="I15" t="s">
+        <v>182</v>
+      </c>
+      <c r="J15" t="s">
+        <v>183</v>
+      </c>
+      <c r="K15">
+        <v>0.0151472518236927</v>
+      </c>
+      <c r="L15">
+        <v>0.02272087773553904</v>
+      </c>
+      <c r="M15" t="s">
+        <v>202</v>
+      </c>
+      <c r="N15">
+        <v>0.574688710741055</v>
+      </c>
+      <c r="O15">
+        <v>0.1744719349694764</v>
+      </c>
+      <c r="P15">
+        <v>0.7448979591836735</v>
+      </c>
+      <c r="Q15">
+        <v>1.819666154360976</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>185</v>
+      </c>
+      <c r="I16" t="s">
+        <v>182</v>
+      </c>
+      <c r="M16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17">
+        <v>48</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" t="s">
+        <v>182</v>
+      </c>
+      <c r="J17" t="s">
+        <v>183</v>
+      </c>
+      <c r="K17">
+        <v>0.005320244326701801</v>
+      </c>
+      <c r="L17">
+        <v>0.0159607329801054</v>
+      </c>
+      <c r="M17" t="s">
+        <v>202</v>
+      </c>
+      <c r="N17">
+        <v>0.8503634914478839</v>
+      </c>
+      <c r="O17">
+        <v>0.238967985783441</v>
+      </c>
+      <c r="P17">
+        <v>0.75</v>
+      </c>
+      <c r="Q17">
+        <v>2.274068422723402</v>
       </c>
     </row>
   </sheetData>
@@ -6098,48 +7118,48 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C4" t="s">
         <v>210</v>
@@ -6147,541 +7167,24 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>221</v>
-      </c>
-      <c r="B8" t="s">
-        <v>222</v>
-      </c>
-      <c r="C8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>223</v>
-      </c>
-      <c r="B9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>225</v>
-      </c>
-      <c r="B10" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B11" t="s">
-        <v>228</v>
-      </c>
-      <c r="C11" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>229</v>
-      </c>
-      <c r="B12" t="s">
-        <v>230</v>
-      </c>
-      <c r="C12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>231</v>
-      </c>
-      <c r="B13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C13" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" t="s">
-        <v>234</v>
-      </c>
-      <c r="C14" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>235</v>
-      </c>
-      <c r="B15" t="s">
-        <v>236</v>
-      </c>
-      <c r="C15" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>238</v>
-      </c>
-      <c r="B16" t="s">
-        <v>239</v>
-      </c>
-      <c r="C16" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>240</v>
-      </c>
-      <c r="B17" t="s">
-        <v>241</v>
-      </c>
-      <c r="C17" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>242</v>
-      </c>
-      <c r="B18" t="s">
-        <v>243</v>
-      </c>
-      <c r="C18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>244</v>
-      </c>
-      <c r="B19" t="s">
-        <v>245</v>
-      </c>
-      <c r="C19" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>246</v>
-      </c>
-      <c r="B20" t="s">
-        <v>247</v>
-      </c>
-      <c r="C20" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>248</v>
-      </c>
-      <c r="B21" t="s">
-        <v>249</v>
-      </c>
-      <c r="C21" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>250</v>
-      </c>
-      <c r="B22" t="s">
-        <v>251</v>
-      </c>
-      <c r="C22" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>252</v>
-      </c>
-      <c r="B23" t="s">
-        <v>253</v>
-      </c>
-      <c r="C23" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>254</v>
-      </c>
-      <c r="B24" t="s">
-        <v>255</v>
-      </c>
-      <c r="C24" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>256</v>
-      </c>
-      <c r="B25" t="s">
-        <v>257</v>
-      </c>
-      <c r="C25" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>258</v>
-      </c>
-      <c r="B26" t="s">
-        <v>259</v>
-      </c>
-      <c r="C26" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>260</v>
-      </c>
-      <c r="B27" t="s">
-        <v>261</v>
-      </c>
-      <c r="C27" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>262</v>
-      </c>
-      <c r="B28" t="s">
-        <v>263</v>
-      </c>
-      <c r="C28" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B29" t="s">
-        <v>265</v>
-      </c>
-      <c r="C29" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>266</v>
-      </c>
-      <c r="B30" t="s">
-        <v>267</v>
-      </c>
-      <c r="C30" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>268</v>
-      </c>
-      <c r="B31" t="s">
-        <v>269</v>
-      </c>
-      <c r="C31" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>270</v>
-      </c>
-      <c r="B32" t="s">
-        <v>271</v>
-      </c>
-      <c r="C32" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>272</v>
-      </c>
-      <c r="B33" t="s">
-        <v>273</v>
-      </c>
-      <c r="C33" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>274</v>
-      </c>
-      <c r="B34" t="s">
-        <v>275</v>
-      </c>
-      <c r="C34" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>276</v>
-      </c>
-      <c r="B35" t="s">
-        <v>277</v>
-      </c>
-      <c r="C35" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>278</v>
-      </c>
-      <c r="B36" t="s">
-        <v>279</v>
-      </c>
-      <c r="C36" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>280</v>
-      </c>
-      <c r="B37" t="s">
-        <v>281</v>
-      </c>
-      <c r="C37" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>282</v>
-      </c>
-      <c r="B38" t="s">
-        <v>283</v>
-      </c>
-      <c r="C38" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>284</v>
-      </c>
-      <c r="B39" t="s">
-        <v>285</v>
-      </c>
-      <c r="C39" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>286</v>
-      </c>
-      <c r="B40" t="s">
-        <v>287</v>
-      </c>
-      <c r="C40" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>288</v>
-      </c>
-      <c r="B41" t="s">
-        <v>289</v>
-      </c>
-      <c r="C41" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>290</v>
-      </c>
-      <c r="B42" t="s">
-        <v>291</v>
-      </c>
-      <c r="C42" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>292</v>
-      </c>
-      <c r="B43" t="s">
-        <v>293</v>
-      </c>
-      <c r="C43" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>294</v>
-      </c>
-      <c r="B44" t="s">
-        <v>295</v>
-      </c>
-      <c r="C44" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>296</v>
-      </c>
-      <c r="B45" t="s">
-        <v>259</v>
-      </c>
-      <c r="C45" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>297</v>
-      </c>
-      <c r="B46" t="s">
-        <v>224</v>
-      </c>
-      <c r="C46" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>298</v>
-      </c>
-      <c r="B47" t="s">
-        <v>299</v>
-      </c>
-      <c r="C47" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>300</v>
-      </c>
-      <c r="B48" t="s">
-        <v>301</v>
-      </c>
-      <c r="C48" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>302</v>
-      </c>
-      <c r="B49" t="s">
-        <v>303</v>
-      </c>
-      <c r="C49" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>304</v>
-      </c>
-      <c r="B50" t="s">
-        <v>305</v>
-      </c>
-      <c r="C50" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>306</v>
-      </c>
-      <c r="B51" t="s">
-        <v>307</v>
-      </c>
-      <c r="C51" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>308</v>
-      </c>
-      <c r="B52" t="s">
-        <v>309</v>
-      </c>
-      <c r="C52" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>310</v>
-      </c>
-      <c r="B53" t="s">
-        <v>311</v>
-      </c>
-      <c r="C53" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/04_Figures/F1/c_data/F1.xlsx
+++ b/04_Figures/F1/c_data/F1.xlsx
@@ -668,7 +668,7 @@
     <t>02_HRvLR/07_Group_Trait_Slopes/c_data/group_trait_slopes.xlsx</t>
   </si>
   <si>
-    <t>f24590e2277ed08b7470c1cb8b4f4eee</t>
+    <t>cd5d6ebfaf5bb2df64f241c5bc674e40</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -677,7 +677,7 @@
     <t>02_HRvLR/02_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
-    <t>30db8bea525624e038076e732efccd5f</t>
+    <t>913e33734a82439181cc7dfdb9ea1917</t>
   </si>
   <si>
     <t>BiocManager</t>

--- a/04_Figures/F1/c_data/F1.xlsx
+++ b/04_Figures/F1/c_data/F1.xlsx
@@ -650,7 +650,7 @@
     <t>02_HRvLR/01_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>eb23e8a1866fdf41427417935863def8</t>
+    <t>f1b9b3d5ee159b256de22fc2b72e89ce</t>
   </si>
   <si>
     <t>variance</t>
@@ -659,7 +659,7 @@
     <t>02_HRvLR/04_Variance/c_data/variance.xlsx</t>
   </si>
   <si>
-    <t>844320d78318f2e845c02f6db890b83d</t>
+    <t>f1ad3960759c75b00d78e1297f45e7ad</t>
   </si>
   <si>
     <t>slopes</t>
@@ -668,7 +668,7 @@
     <t>02_HRvLR/07_Group_Trait_Slopes/c_data/group_trait_slopes.xlsx</t>
   </si>
   <si>
-    <t>cd5d6ebfaf5bb2df64f241c5bc674e40</t>
+    <t>b2284ace62d57e411d12c11b4087bb9c</t>
   </si>
   <si>
     <t>set_tests</t>
